--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R85e2635a033c4b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Raf559c0e99b345ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R6add47113ffe49db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R2525127df7c94921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R3aed19cbe7cf4e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R2d7d84cd81c64b61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rc9fc4934fc7d417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Raa5736e6a1d6402f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -554,7 +554,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Status atualizado em 11/10/2026 | fechamento funcional de 13/09/2026</x:v>
+        <x:v>Status atualizado em 10/10/2026 | fechamento funcional de 13/09/2026</x:v>
       </x:c>
       <x:c r="B3" s="2" t="n"/>
       <x:c r="C3" s="2" t="n"/>
@@ -632,7 +632,7 @@
       </x:c>
       <x:c r="B7" s="22" t="n">
         <x:f>COUNTIFS('Tarefas'!$D$6:$D$132,"Planejamento",'Tarefas'!$G$6:$G$132,1)</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="11" t="inlineStr">
         <x:is>
@@ -660,7 +660,7 @@
       </x:c>
       <x:c r="B8" s="27" t="n">
         <x:f>SUM('Tarefas'!$M$6:$M$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.03937007874015748</x:v>
+        <x:v>0.047244094488188976</x:v>
       </x:c>
       <x:c r="C8" s="11" t="inlineStr">
         <x:is>
@@ -815,7 +815,7 @@
       </x:c>
       <x:c r="C14" s="28" t="n">
         <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.375</x:v>
       </x:c>
       <x:c r="D14" s="2" t="n"/>
       <x:c r="E14" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>BK-000 e BK-004 auditadas em 10–11/10; 125 tarefas ainda aguardam revisão. Regra definida não equivale a implementação concluída.</x:v>
+        <x:v>BK-000, BK-004 e BK-005 auditadas nesta rodada; 124 tarefas ainda aguardam revisão. Regra definida não equivale a implementação concluída.</x:v>
       </x:c>
       <x:c r="B33" s="2" t="n"/>
       <x:c r="C33" s="2" t="n"/>
@@ -1662,16 +1662,18 @@
         <x:v>Planejamento</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Concluída</x:v>
       </x:c>
       <x:c r="F11" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="32" t="n">
         <x:f>IF(AND(E11="Concluída",H11&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>Cenários de aceite e tratamento de ambiguidade registrados nesta tarefa a partir da regra C-01 aprovada; não houve alteração de código nem execução de testes.</x:v>
+      </x:c>
       <x:c r="I11" s="11" t="str">
         <x:v>Majucau / Financeiro</x:v>
       </x:c>
@@ -1684,7 +1686,7 @@
       </x:c>
       <x:c r="M11" s="11" t="n">
         <x:f>F11*G11</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" customHeight="1">
@@ -6575,7 +6577,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbadaebe5b9749f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c84d42adf1c4a4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6927,7 +6929,7 @@
         <x:v>Aplicar a definição vigente; execução, evidência e aceite são registrados nas tarefas relacionadas.</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
-        <x:v>Marcar divergência e manter o título sem baixa até a análise. Casos complementares serão detalhados em BK-005.</x:v>
+        <x:v>Qualquer diferença, inclusive R$ 0,01, marca divergência e mantém o título sem baixa até análise. Cenários de aceite, tratamento de ambiguidade e proteção contra duplicidade estão detalhados em BK-005.</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
         <x:v>C_Conflitos!A3:L3; Fechamento das questões ainda tratadas como abertas — 13/09/2026</x:v>
@@ -9808,7 +9810,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f77f6f26ffc4123"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6416207027934f65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10457,7 +10459,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rced378c258b24ae6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a2944d3c0214580"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R3aed19cbe7cf4e93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R2d7d84cd81c64b61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rc9fc4934fc7d417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Raa5736e6a1d6402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R4e199a25579d45ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rdf85e673887d4172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R3ac31b6bf8e74a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rb516162f4b5842f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -632,7 +632,7 @@
       </x:c>
       <x:c r="B7" s="22" t="n">
         <x:f>COUNTIFS('Tarefas'!$D$6:$D$132,"Planejamento",'Tarefas'!$G$6:$G$132,1)</x:f>
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="11" t="inlineStr">
         <x:is>
@@ -660,7 +660,7 @@
       </x:c>
       <x:c r="B8" s="27" t="n">
         <x:f>SUM('Tarefas'!$M$6:$M$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.047244094488188976</x:v>
+        <x:v>0.03937007874015748</x:v>
       </x:c>
       <x:c r="C8" s="11" t="inlineStr">
         <x:is>
@@ -815,7 +815,7 @@
       </x:c>
       <x:c r="C14" s="28" t="n">
         <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.375</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="D14" s="2" t="n"/>
       <x:c r="E14" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>BK-000, BK-004 e BK-005 auditadas nesta rodada; 124 tarefas ainda aguardam revisão. Regra definida não equivale a implementação concluída.</x:v>
+        <x:v>BK-000, BK-002, BK-004 e BK-005 auditadas; BK-001 aguarda decisão sobre arquivos originais; 122 tarefas aguardam revisão. Regra definida não equivale a implementação concluída.</x:v>
       </x:c>
       <x:c r="B33" s="2" t="n"/>
       <x:c r="C33" s="2" t="n"/>
@@ -1500,29 +1500,31 @@
         <x:v>Planejamento</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>Concluída</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F7" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="32" t="n">
         <x:f>IF(AND(E7="Concluída",H7&lt;&gt;""),1,0)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>MAJUCAU_ANALISE_E_DECISOES_v0.md — inventário e análise; inspeção dos materiais e GitHub nesta sessão. Evidência original preservada na versão 0; esta revisão não altera a conclusão desse levantamento.</x:v>
+        <x:v>Inventário histórico registra 16 PNGs, 15 imagens únicas, 20 abas, T10 duplicada e materiais ausentes; a extração tem 20 entradas de aba e as versões v0/v1/v2 estão preservadas. Os hashes dos originais constam em FONTES.md, mas sources/private/material-original não existe neste checkout e os nomes exatos não foram encontrados em Downloads. A responsável foi consultada se enviará os originais ou aceita hashes/extrações; resposta pendente. BK-001 permanece aberta até a decisão.</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
         <x:v>Produto + UX</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
-      <x:c r="K7" s="11" t="str"/>
+      <x:c r="K7" s="11" t="str">
+        <x:v>Aguardar orientação sobre os originais: envio para arquivo privado local ou aceitação de hashes e extrações como suficientes.</x:v>
+      </x:c>
       <x:c r="L7" s="11" t="str">
-        <x:v>Pacote fornecido; manifesto de arquivos; Consolidação 13/09/2026, consolidação integral; Fechamento vigente 13/09/2026, integral</x:v>
+        <x:v>docs/planejamento/FONTES.md; docs/source/README.md; docs/planejamento/work/source_extract; revision_v1.json; revision_v2.json</x:v>
       </x:c>
       <x:c r="M7" s="11" t="n">
         <x:f>F7*G7</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
@@ -1549,15 +1551,17 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>MAJUCAU_ANALISE_E_DECISOES_v0.md — inventário e análise; inspeção dos materiais e GitHub nesta sessão. Evidência original preservada na versão 0; esta revisão não altera a conclusão desse levantamento.</x:v>
+        <x:v>Auditoria pública somente de leitura em 10/10/2026: repositório público, branch padrão main no commit 39f8630390936717b2500c8b7ce923dc138cca72; branch de trabalho codex/majucau-artifact-consolidation em b94bb3a, mesma ponta remota, 178 commits à frente e zero atrás de main. A API retornou zero issues e cinco pull requests abertos e não mesclados (#1–#5), todos em outras branches. A afirmação de repositório vazio em v0 é histórica. A responsável confirmou que não há outro clone, servidor ou ambiente de trabalho fora deste checkout; o código é controlado somente pelo Git/GitHub. Nenhuma branch foi mesclada e nenhum teste foi executado.</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>Arquitetura</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str"/>
-      <x:c r="K8" s="10" t="str"/>
+      <x:c r="K8" s="10" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>GitHub majucau /contents e /commits</x:v>
+        <x:v>GitHub REST: repos/guilhermejacyzin/majucau, branches/main, issues?state=all, pulls?state=all; git ls-remote origin; comparação origin/main..HEAD</x:v>
       </x:c>
       <x:c r="M8" s="10" t="n">
         <x:f>F8*G8</x:f>
@@ -6577,7 +6581,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c84d42adf1c4a4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03b99404c46340d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9810,7 +9814,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6416207027934f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R954bf805c8a14ed8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10459,7 +10463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a2944d3c0214580"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d93b637c97a4068"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R4e199a25579d45ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rdf85e673887d4172"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R3ac31b6bf8e74a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rb516162f4b5842f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R0b92ed591fed4f99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R41bdbb3be8314419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R8e748c5c297d43b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Racebe127eac54b99"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="164" formatCode="0.0%"/>
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="0%"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
+    <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -84,106 +86,94 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -195,99 +185,32 @@
         <x:color rgb="FFA12622"/>
       </x:font>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFDE4E0"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
   </x:dxfs>
-  <x:colors>
-    <x:indexedColors>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008000"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00808000"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="00C0C0C0"/>
-      <x:rgbColor rgb="00808080"/>
-      <x:rgbColor rgb="009999FF"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00FFFFCC"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00660066"/>
-      <x:rgbColor rgb="00FF8080"/>
-      <x:rgbColor rgb="000066CC"/>
-      <x:rgbColor rgb="00CCCCFF"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="0000CCFF"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00CCFFCC"/>
-      <x:rgbColor rgb="00FFFF99"/>
-      <x:rgbColor rgb="0099CCFF"/>
-      <x:rgbColor rgb="00FF99CC"/>
-      <x:rgbColor rgb="00CC99FF"/>
-      <x:rgbColor rgb="00FFCC99"/>
-      <x:rgbColor rgb="003366FF"/>
-      <x:rgbColor rgb="0033CCCC"/>
-      <x:rgbColor rgb="0099CC00"/>
-      <x:rgbColor rgb="00FFCC00"/>
-      <x:rgbColor rgb="00FF9900"/>
-      <x:rgbColor rgb="00FF6600"/>
-      <x:rgbColor rgb="00666699"/>
-      <x:rgbColor rgb="00969696"/>
-      <x:rgbColor rgb="00003366"/>
-      <x:rgbColor rgb="00339966"/>
-      <x:rgbColor rgb="00003300"/>
-      <x:rgbColor rgb="00333300"/>
-      <x:rgbColor rgb="00993300"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00333399"/>
-      <x:rgbColor rgb="00333333"/>
-    </x:indexedColors>
-  </x:colors>
 </x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MajucauTarefas" displayName="MajucauTarefas" ref="A5:M132" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MajucauTarefas" displayName="MajucauTarefas" ref="A5:N132" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Fase"/>
     <x:tableColumn id="3" name="Tarefa"/>
     <x:tableColumn id="4" name="Natureza"/>
     <x:tableColumn id="5" name="Situação"/>
     <x:tableColumn id="6" name="Peso"/>
-    <x:tableColumn id="7" name="Evolução"/>
+    <x:tableColumn id="7" name="Evolução estimada"/>
     <x:tableColumn id="8" name="Evidência de aceite"/>
     <x:tableColumn id="9" name="Responsável sugerido"/>
     <x:tableColumn id="10" name="Dependências"/>
     <x:tableColumn id="11" name="Decisões a acompanhar"/>
     <x:tableColumn id="12" name="Referências"/>
-    <x:tableColumn id="13" name="Peso concluído"/>
+    <x:tableColumn id="13" name="Peso com aceite"/>
+    <x:tableColumn id="14" name="Peso da evolução"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -519,769 +442,638 @@
   <x:sheetPr>
     <x:tabColor rgb="FF0B3346"/>
   </x:sheetPr>
-  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36.880001068115234" customWidth="1"/>
-    <x:col min="2" max="2" width="15.630000114440918" customWidth="1"/>
-    <x:col min="3" max="3" width="21.25" customWidth="1"/>
-    <x:col min="4" max="4" width="3.5" customWidth="1"/>
-    <x:col min="5" max="5" width="42.5" customWidth="1"/>
-    <x:col min="6" max="6" width="37.5" customWidth="1"/>
-    <x:col min="7" max="7" width="18.75" customWidth="1"/>
+    <x:col min="1" max="1" width="36.880001068115234" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="3.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42.5" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="2" t="n"/>
-      <x:c r="B1" s="2" t="n"/>
-      <x:c r="C1" s="2" t="n"/>
-      <x:c r="D1" s="2" t="n"/>
-      <x:c r="E1" s="2" t="n"/>
-      <x:c r="F1" s="2" t="n"/>
-      <x:c r="G1" s="2" t="n"/>
+      <x:c r="A1" s="2"/>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Majucau — evolução do backlog</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="n"/>
-      <x:c r="C2" s="2" t="n"/>
-      <x:c r="D2" s="2" t="n"/>
-      <x:c r="E2" s="2" t="n"/>
-      <x:c r="F2" s="2" t="n"/>
-      <x:c r="G2" s="2" t="n"/>
+      <x:c r="A2" s="3" t="str">
+        <x:v>Majucau — evolução do backlog</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Status atualizado em 10/10/2026 | fechamento funcional de 13/09/2026</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="n"/>
-      <x:c r="C3" s="2" t="n"/>
-      <x:c r="D3" s="2" t="n"/>
-      <x:c r="E3" s="2" t="n"/>
-      <x:c r="F3" s="2" t="n"/>
-      <x:c r="G3" s="2" t="n"/>
+        <x:v>Status atualizado em 11/10/2026 | fechamento funcional de 13/09/2026</x:v>
+      </x:c>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="2" t="n"/>
-      <x:c r="B4" s="2" t="n"/>
-      <x:c r="C4" s="2" t="n"/>
-      <x:c r="D4" s="2" t="n"/>
-      <x:c r="E4" s="2" t="n"/>
-      <x:c r="F4" s="2" t="n"/>
-      <x:c r="G4" s="2" t="n"/>
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Medida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Valor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Interpretação</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="2" t="n"/>
-      <x:c r="E5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Decisões já recebidas</x:t>
-        </x:is>
+      <x:c r="A5" s="8" t="str">
+        <x:v>Medida</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>Valor</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>Interpretação</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="8" t="str">
+        <x:v>Decisões já recebidas</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str"/>
       <x:c r="G5" s="8" t="str"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tarefas no catálogo</x:t>
-        </x:is>
+      <x:c r="A6" s="2" t="str">
+        <x:v>Tarefas no catálogo</x:v>
       </x:c>
       <x:c r="B6" s="22" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Escopo provisório</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="2" t="n"/>
-      <x:c r="E6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Empresa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Somente Majucau</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="2" t="n"/>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Escopo provisório</x:v>
+      </x:c>
+      <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2" t="str">
+        <x:v>Empresa</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="str">
+        <x:v>Somente Majucau</x:v>
+      </x:c>
+      <x:c r="G6" s="2"/>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Levantamentos concluídos</x:t>
-        </x:is>
+      <x:c r="A7" s="2" t="str">
+        <x:v>Levantamentos concluídos</x:v>
       </x:c>
       <x:c r="B7" s="22" t="n">
-        <x:f>COUNTIFS('Tarefas'!$D$6:$D$132,"Planejamento",'Tarefas'!$G$6:$G$132,1)</x:f>
+        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$D$6:$D$132,"Planejamento")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Com evidência</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="2" t="n"/>
-      <x:c r="E7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Usuários</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3 diretores</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="2" t="n"/>
+      <x:c r="C7" s="11" t="str">
+        <x:v>Com evidência de aceite</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2" t="str">
+        <x:v>Usuários</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="str">
+        <x:v>3 diretores</x:v>
+      </x:c>
+      <x:c r="G7" s="2"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Conclusão por peso</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="27" t="n">
-        <x:f>SUM('Tarefas'!$M$6:$M$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.03937007874015748</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Peso inicial = 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="2" t="n"/>
-      <x:c r="E8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hospedagem</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Atual local; destino privado centralizado</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="2" t="n"/>
+      <x:c r="A8" s="2" t="str">
+        <x:v>Evolução estimada por peso</x:v>
+      </x:c>
+      <x:c r="B8" s="23" t="n">
+        <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
+        <x:v>0.07165354330708662</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>Estimativa; não é prontidão</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2" t="str">
+        <x:v>Hospedagem</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="str">
+        <x:v>Atual local; destino privado centralizado</x:v>
+      </x:c>
+      <x:c r="G8" s="2"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tarefas de desenvolvimento concluídas</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="27" t="n">
+      <x:c r="A9" s="2" t="str">
+        <x:v>Desenvolvimento aceito</x:v>
+      </x:c>
+      <x:c r="B9" s="23" t="n">
         <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$D$6:$D$132,"Desenvolvimento")/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$D$6:$D$132,"Desenvolvimento")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Com evidência no rastreador</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="2" t="n"/>
-      <x:c r="E9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Primeira produção</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Todos os módulos confirmados</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="2" t="n"/>
+        <x:v>0.01020408163265306</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Somente concluído com evidência</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2" t="str">
+        <x:v>Primeira produção</x:v>
+      </x:c>
+      <x:c r="F9" s="2" t="str">
+        <x:v>Todos os módulos confirmados</x:v>
+      </x:c>
+      <x:c r="G9" s="2"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Frentes técnicas</x:t>
-        </x:is>
+      <x:c r="A10" s="2" t="str">
+        <x:v>Frentes técnicas</x:v>
       </x:c>
       <x:c r="B10" s="22" t="n">
         <x:f>COUNTIFS('Decisoes'!$I$6:$I$113,"Homologação técnica")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HT: execução futura</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="2" t="n"/>
-      <x:c r="E10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pagamento diferente</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Divergência, sem baixa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="2" t="n"/>
+      <x:c r="C10" s="11" t="str">
+        <x:v>HT: execução futura</x:v>
+      </x:c>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2" t="str">
+        <x:v>Pagamento diferente</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="str">
+        <x:v>Divergência, sem baixa</x:v>
+      </x:c>
+      <x:c r="G10" s="2"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="2" t="n"/>
-      <x:c r="B11" s="2" t="n"/>
-      <x:c r="C11" s="2" t="n"/>
-      <x:c r="D11" s="2" t="n"/>
-      <x:c r="E11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Semana crítica</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Maior total de despesas</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="2" t="n"/>
+      <x:c r="A11" s="2" t="str">
+        <x:v>Tarefas aceitas com evidência</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="n">
+        <x:f>COUNTIFS('Tarefas'!$E$6:$E$132,"Concluída",'Tarefas'!$H$6:$H$132,"&lt;&gt;")</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Contagem de entregas concluídas</x:v>
+      </x:c>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2" t="str">
+        <x:v>Caixa da aplicação</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="str">
+        <x:v>Seguir estrutura enviada; fluxo consolidado D0–D+60</x:v>
+      </x:c>
+      <x:c r="G11" s="2"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Avanço por fase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="2" t="n"/>
-      <x:c r="C12" s="2" t="n"/>
-      <x:c r="D12" s="2" t="n"/>
-      <x:c r="E12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DRE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculada pelo Majucau; Bling para comparação</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="2" t="n"/>
+      <x:c r="A12" s="24" t="str">
+        <x:v>Avanço por fase</x:v>
+      </x:c>
+      <x:c r="B12" s="2"/>
+      <x:c r="C12" s="2"/>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2" t="str">
+        <x:v>DRE</x:v>
+      </x:c>
+      <x:c r="F12" s="2" t="str">
+        <x:v>Calculada pelo Majucau; Bling para comparação</x:v>
+      </x:c>
+      <x:c r="G12" s="2"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tarefas</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Concluído</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="2" t="n"/>
-      <x:c r="E13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cards EBIT/EBITDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No lugar do card inferior UNMAPPED</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="2" t="n"/>
+      <x:c r="A13" s="8" t="str">
+        <x:v>Fase</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>Tarefas</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>Evolução estimada</x:v>
+      </x:c>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2" t="str">
+        <x:v>Cards EBIT/EBITDA</x:v>
+      </x:c>
+      <x:c r="F13" s="2" t="str">
+        <x:v>No espaço aprovado no lugar de UNMAPPED</x:v>
+      </x:c>
+      <x:c r="G13" s="2"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">00 Descoberta e decisões</x:t>
-        </x:is>
+      <x:c r="A14" s="9" t="str">
+        <x:v>00 Descoberta e decisões</x:v>
       </x:c>
       <x:c r="B14" s="9" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A14)</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.3125</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="n"/>
-      <x:c r="E14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cards CAPEX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pago no mês e acumulado; fora do lucro</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="2" t="n"/>
+      <x:c r="C14" s="26" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
+        <x:v>0.36562500000000003</x:v>
+      </x:c>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2" t="str">
+        <x:v>Cards CAPEX</x:v>
+      </x:c>
+      <x:c r="F14" s="2" t="str">
+        <x:v>Pago no mês e acumulado; fora do lucro</x:v>
+      </x:c>
+      <x:c r="G14" s="2"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">01 Arquitetura e UX</x:t>
-        </x:is>
+      <x:c r="A15" s="2" t="str">
+        <x:v>01 Arquitetura e UX</x:v>
       </x:c>
       <x:c r="B15" s="2" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C15" s="29" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="2" t="n"/>
-      <x:c r="E15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Balanço Patrimonial</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fora do escopo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="2" t="n"/>
+      <x:c r="C15" s="25" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2" t="str">
+        <x:v>Balanço Patrimonial</x:v>
+      </x:c>
+      <x:c r="F15" s="2" t="str">
+        <x:v>Fora do escopo</x:v>
+      </x:c>
+      <x:c r="G15" s="2"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">02 Fundação do projeto</x:t>
-        </x:is>
+      <x:c r="A16" s="9" t="str">
+        <x:v>02 Fundação do projeto</x:v>
       </x:c>
       <x:c r="B16" s="9" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A16)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A16)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="n"/>
-      <x:c r="E16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Referências</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Última versão aprovada</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="2" t="n"/>
+      <x:c r="C16" s="26" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A16)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A16)</x:f>
+        <x:v>0.35714285714285715</x:v>
+      </x:c>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2" t="str">
+        <x:v>Referências</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="str">
+        <x:v>Última versão aprovada</x:v>
+      </x:c>
+      <x:c r="G16" s="2"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">03 Identidade e configurações</x:t>
-        </x:is>
+      <x:c r="A17" s="2" t="str">
+        <x:v>03 Identidade e configurações</x:v>
       </x:c>
       <x:c r="B17" s="2" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A17)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A17)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="2" t="n"/>
-      <x:c r="E17" s="24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Como atualizar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="2" t="n"/>
-      <x:c r="G17" s="2" t="n"/>
+      <x:c r="C17" s="25" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A17)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A17)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="24" t="str">
+        <x:v>Como atualizar</x:v>
+      </x:c>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
     </x:row>
     <x:row r="18" ht="29" customHeight="1">
-      <x:c r="A18" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">04 Dados e integrações</x:t>
-        </x:is>
+      <x:c r="A18" s="9" t="str">
+        <x:v>04 Dados e integrações</x:v>
       </x:c>
       <x:c r="B18" s="9" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A18)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A18)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="2" t="n"/>
-      <x:c r="E18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Na aba Tarefas, atualize Situação e Evidência de aceite.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="2" t="n"/>
-      <x:c r="G18" s="2" t="n"/>
+      <x:c r="C18" s="26" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A18)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A18)</x:f>
+        <x:v>0.03666666666666667</x:v>
+      </x:c>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2" t="str">
+        <x:v>Na aba Tarefas, atualize Situação, Evolução estimada e Evidência.</x:v>
+      </x:c>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
     </x:row>
     <x:row r="19" ht="29" customHeight="1">
-      <x:c r="A19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">05 Tesouraria e conciliação</x:t>
-        </x:is>
+      <x:c r="A19" s="2" t="str">
+        <x:v>05 Tesouraria e conciliação</x:v>
       </x:c>
       <x:c r="B19" s="2" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A19)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C19" s="29" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A19)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="2" t="n"/>
-      <x:c r="E19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Concluída + evidência preenchida produz 100% na tarefa.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="2" t="n"/>
-      <x:c r="G19" s="2" t="n"/>
+      <x:c r="C19" s="25" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A19)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A19)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2" t="str">
+        <x:v>Concluída com evidência conta como aceite comprovado.</x:v>
+      </x:c>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
     </x:row>
     <x:row r="20" ht="29" customHeight="1">
-      <x:c r="A20" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">06 Resultados, perdas e aplicações</x:t>
-        </x:is>
+      <x:c r="A20" s="9" t="str">
+        <x:v>06 Resultados, perdas e aplicações</x:v>
       </x:c>
       <x:c r="B20" s="9" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A20)</x:f>
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="28" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A20)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="2" t="n"/>
-      <x:c r="E20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Em andamento indica atividade; não conta como entrega concluída.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="2" t="n"/>
-      <x:c r="G20" s="2" t="n"/>
+      <x:c r="C20" s="26" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A20)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A20)</x:f>
+        <x:v>0.014285714285714287</x:v>
+      </x:c>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2" t="str">
+        <x:v>A evolução estimada aparece antes do aceite final.</x:v>
+      </x:c>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
     </x:row>
     <x:row r="21" ht="29" customHeight="1">
-      <x:c r="A21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">07 Estoque, produção e compras</x:t>
-        </x:is>
+      <x:c r="A21" s="2" t="str">
+        <x:v>07 Estoque, produção e compras</x:v>
       </x:c>
       <x:c r="B21" s="2" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A21)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C21" s="29" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A21)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="2" t="n"/>
-      <x:c r="E21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Peso inicial 1 mede quantidade, sem estimativa de esforço.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="2" t="n"/>
-      <x:c r="G21" s="2" t="n"/>
+      <x:c r="C21" s="25" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A21)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A21)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2" t="str">
+        <x:v>A média global é estimativa do backlog; não é prontidão para produção.</x:v>
+      </x:c>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
     </x:row>
     <x:row r="22" ht="29" customHeight="1">
-      <x:c r="A22" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">08 Projeções e cenários</x:t>
-        </x:is>
+      <x:c r="A22" s="9" t="str">
+        <x:v>08 Projeções e cenários</x:v>
       </x:c>
       <x:c r="B22" s="9" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A22)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C22" s="28" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A22)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="2" t="n"/>
-      <x:c r="E22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Após estimar com a equipe, revise os pesos e registre a mudança.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F22" s="2" t="n"/>
-      <x:c r="G22" s="2" t="n"/>
+      <x:c r="C22" s="26" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A22)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A22)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2" t="str">
+        <x:v>Peso inicial 1 mede quantidade, sem estimativa de esforço.</x:v>
+      </x:c>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
     </x:row>
     <x:row r="23" ht="29" customHeight="1">
-      <x:c r="A23" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">09 Controle e visão executiva</x:t>
-        </x:is>
+      <x:c r="A23" s="2" t="str">
+        <x:v>09 Controle e visão executiva</x:v>
       </x:c>
       <x:c r="B23" s="2" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A23)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C23" s="29" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A23)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="2" t="n"/>
-      <x:c r="E23" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">As fórmulas consideram todas as linhas atuais, mesmo filtradas.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F23" s="2" t="n"/>
-      <x:c r="G23" s="2" t="n"/>
+      <x:c r="C23" s="25" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A23)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A23)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2" t="str">
+        <x:v>Após estimar com a equipe, revise os pesos e registre a mudança.</x:v>
+      </x:c>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
     </x:row>
     <x:row r="24" ht="29" customHeight="1">
-      <x:c r="A24" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10 Verificação integrada</x:t>
-        </x:is>
+      <x:c r="A24" s="9" t="str">
+        <x:v>10 Verificação integrada</x:v>
       </x:c>
       <x:c r="B24" s="9" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A24)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A24)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="2" t="n"/>
-      <x:c r="E24" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ao incluir tarefas, ampliar tabela e fórmulas de resumo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="2" t="n"/>
-      <x:c r="G24" s="2" t="n"/>
+      <x:c r="C24" s="26" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A24)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A24)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2" t="str">
+        <x:v>As fórmulas consideram todas as linhas atuais, mesmo filtradas.</x:v>
+      </x:c>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
     </x:row>
     <x:row r="25" ht="29" customHeight="1">
-      <x:c r="A25" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">11 Instalação, produção e sustentação</x:t>
-        </x:is>
+      <x:c r="A25" s="2" t="str">
+        <x:v>11 Instalação, produção e sustentação</x:v>
       </x:c>
       <x:c r="B25" s="2" t="n">
         <x:f>COUNTIFS('Tarefas'!$B$6:$B$132,A25)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C25" s="29" t="n">
-        <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$B$6:$B$132,A25)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="2" t="n"/>
-      <x:c r="E25" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Percentual do controle; não mede a conclusão real do produto.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F25" s="2" t="n"/>
-      <x:c r="G25" s="2" t="n"/>
+      <x:c r="C25" s="25" t="n">
+        <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A25)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2" t="str">
+        <x:v>Ao incluir tarefas, ampliar tabela e fórmulas de resumo.</x:v>
+      </x:c>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
     </x:row>
     <x:row r="26" ht="29" customHeight="1">
-      <x:c r="A26" s="2" t="n"/>
-      <x:c r="B26" s="2" t="n"/>
-      <x:c r="C26" s="2" t="n"/>
-      <x:c r="D26" s="2" t="n"/>
-      <x:c r="E26" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Detalhamento passo a passo fica no documento pelo ID BK.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F26" s="2" t="n"/>
-      <x:c r="G26" s="2" t="n"/>
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2" t="str">
+        <x:v>Detalhamento passo a passo fica no documento pelo ID BK.</x:v>
+      </x:c>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
     </x:row>
     <x:row r="27" ht="29" customHeight="1">
-      <x:c r="A27" s="2" t="n"/>
-      <x:c r="B27" s="2" t="n"/>
-      <x:c r="C27" s="2" t="n"/>
-      <x:c r="D27" s="2" t="n"/>
-      <x:c r="E27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Não existe atualização automática de atividade no GitHub.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F27" s="2" t="n"/>
-      <x:c r="G27" s="2" t="n"/>
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
+      <x:c r="C27" s="2"/>
+      <x:c r="D27" s="2"/>
+      <x:c r="E27" s="2" t="str">
+        <x:v>Não existe atualização automática de atividade no GitHub.</x:v>
+      </x:c>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Responsáveis são papéis sugeridos; prazo e esforço aguardam a equipe.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B28" s="2" t="n"/>
-      <x:c r="C28" s="2" t="n"/>
-      <x:c r="D28" s="2" t="n"/>
-      <x:c r="E28" s="2" t="n"/>
-      <x:c r="F28" s="2" t="n"/>
-      <x:c r="G28" s="2" t="n"/>
+      <x:c r="A28" s="2" t="str">
+        <x:v>Responsáveis são papéis sugeridos; prazo e esforço aguardam a equipe.</x:v>
+      </x:c>
+      <x:c r="B28" s="2"/>
+      <x:c r="C28" s="2"/>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="2" t="n"/>
-      <x:c r="B29" s="2" t="n"/>
-      <x:c r="C29" s="2" t="n"/>
-      <x:c r="D29" s="2" t="n"/>
-      <x:c r="E29" s="2" t="n"/>
-      <x:c r="F29" s="2" t="n"/>
-      <x:c r="G29" s="2" t="n"/>
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fonte: imagens e planilha MAJUCAU_CONSOLIDACAO_DEV_GATE_RC3_CEI_CONFIGURACOES_T16_T17.xlsx fornecidas pelo usuário.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B30" s="2" t="n"/>
-      <x:c r="C30" s="2" t="n"/>
-      <x:c r="D30" s="2" t="n"/>
-      <x:c r="E30" s="2" t="n"/>
-      <x:c r="F30" s="2" t="n"/>
-      <x:c r="G30" s="2" t="n"/>
+      <x:c r="A30" s="4" t="str">
+        <x:v>Fonte: imagens e planilha MAJUCAU_CONSOLIDACAO_DEV_GATE_RC3_CEI_CONFIGURACOES_T16_T17.xlsx fornecidas pelo usuário.</x:v>
+      </x:c>
+      <x:c r="B30" s="2"/>
+      <x:c r="C30" s="2"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fechamento de 13/09/2026; decisões posteriores registradas no G0-DECISION-REGISTER.md até 10/10/2026.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" s="2" t="n"/>
-      <x:c r="C31" s="2" t="n"/>
-      <x:c r="D31" s="2" t="n"/>
-      <x:c r="E31" s="2" t="n"/>
-      <x:c r="F31" s="2" t="n"/>
-      <x:c r="G31" s="2" t="n"/>
+      <x:c r="A31" s="4" t="str">
+        <x:v>Fechamento de 13/09/2026; decisões posteriores registradas no G0-DECISION-REGISTER.md até 11/10/2026.</x:v>
+      </x:c>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="2" t="n"/>
-      <x:c r="B32" s="2" t="n"/>
-      <x:c r="C32" s="2" t="n"/>
-      <x:c r="D32" s="2" t="n"/>
-      <x:c r="E32" s="2" t="n"/>
-      <x:c r="F32" s="2" t="n"/>
-      <x:c r="G32" s="2" t="n"/>
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>BK-000, BK-002, BK-004 e BK-005 auditadas; BK-001 aguarda decisão sobre arquivos originais; 122 tarefas aguardam revisão. Regra definida não equivale a implementação concluída.</x:v>
-      </x:c>
-      <x:c r="B33" s="2" t="n"/>
-      <x:c r="C33" s="2" t="n"/>
-      <x:c r="D33" s="2" t="n"/>
-      <x:c r="E33" s="2" t="n"/>
-      <x:c r="F33" s="2" t="n"/>
-      <x:c r="G33" s="2" t="n"/>
+        <x:v>Backlog em 11/10/2026: 6 concluídas, 10 em andamento e 111 não iniciadas. Estimativa média: 7,2%; restantes 92,8%. BK-001 aguarda decisão sobre arquivos originais. Regra definida não equivale a implementação concluída.</x:v>
+      </x:c>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D-1: análise/conciliação normal até ontem; agenda futura continua na projeção.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B34" s="2" t="n"/>
-      <x:c r="C34" s="2" t="n"/>
-      <x:c r="D34" s="2" t="n"/>
-      <x:c r="E34" s="2" t="n"/>
-      <x:c r="F34" s="2" t="n"/>
-      <x:c r="G34" s="2" t="n"/>
+      <x:c r="A34" s="2" t="str">
+        <x:v>D-1: análise/conciliação normal até ontem; agenda futura continua na projeção.</x:v>
+      </x:c>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nenhuma regra foi reaberta nesta auditoria. Paginação do Bling e outras pendências técnicas continuam em verificação.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B35" s="2" t="n"/>
-      <x:c r="C35" s="2" t="n"/>
-      <x:c r="D35" s="2" t="n"/>
-      <x:c r="E35" s="2" t="n"/>
-      <x:c r="F35" s="2" t="n"/>
-      <x:c r="G35" s="2" t="n"/>
+      <x:c r="A35" s="2" t="str">
+        <x:v>Nenhuma regra foi reaberta nesta auditoria. Paginação do Bling e outras pendências técnicas continuam em verificação.</x:v>
+      </x:c>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
-      <x:c r="A36" s="2" t="n"/>
-      <x:c r="B36" s="2" t="n"/>
-      <x:c r="C36" s="2" t="n"/>
-      <x:c r="D36" s="2" t="n"/>
-      <x:c r="E36" s="2" t="n"/>
-      <x:c r="F36" s="2" t="n"/>
-      <x:c r="G36" s="2" t="n"/>
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="2" t="n"/>
-      <x:c r="B37" s="2" t="n"/>
-      <x:c r="C37" s="2" t="n"/>
-      <x:c r="D37" s="2" t="n"/>
-      <x:c r="E37" s="2" t="n"/>
-      <x:c r="F37" s="2" t="n"/>
-      <x:c r="G37" s="2" t="n"/>
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
-      <x:c r="A38" s="2" t="n"/>
-      <x:c r="B38" s="2" t="n"/>
-      <x:c r="C38" s="2" t="n"/>
-      <x:c r="D38" s="2" t="n"/>
-      <x:c r="E38" s="2" t="n"/>
-      <x:c r="F38" s="2" t="n"/>
-      <x:c r="G38" s="2" t="n"/>
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
     </x:row>
     <x:row r="39" ht="28" customHeight="1">
-      <x:c r="A39" s="2" t="n"/>
-      <x:c r="B39" s="2" t="n"/>
-      <x:c r="C39" s="2" t="n"/>
-      <x:c r="D39" s="2" t="n"/>
-      <x:c r="E39" s="2" t="n"/>
-      <x:c r="F39" s="2" t="n"/>
-      <x:c r="G39" s="2" t="n"/>
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
-      <x:c r="A40" s="2" t="n"/>
-      <x:c r="B40" s="2" t="n"/>
-      <x:c r="C40" s="2" t="n"/>
-      <x:c r="D40" s="2" t="n"/>
-      <x:c r="E40" s="2" t="n"/>
-      <x:c r="F40" s="2" t="n"/>
-      <x:c r="G40" s="2" t="n"/>
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
-      <x:c r="A41" s="2" t="n"/>
-      <x:c r="B41" s="2" t="n"/>
-      <x:c r="C41" s="2" t="n"/>
-      <x:c r="D41" s="2" t="n"/>
-      <x:c r="E41" s="2" t="n"/>
-      <x:c r="F41" s="2" t="n"/>
-      <x:c r="G41" s="2" t="n"/>
+      <x:c r="A41" s="2"/>
+      <x:c r="B41" s="2"/>
+      <x:c r="C41" s="2"/>
+      <x:c r="D41" s="2"/>
+      <x:c r="E41" s="2"/>
+      <x:c r="F41" s="2"/>
+      <x:c r="G41" s="2"/>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
-      <x:c r="A42" s="2" t="n"/>
-      <x:c r="B42" s="2" t="n"/>
-      <x:c r="C42" s="2" t="n"/>
-      <x:c r="D42" s="2" t="n"/>
-      <x:c r="E42" s="2" t="n"/>
-      <x:c r="F42" s="2" t="n"/>
-      <x:c r="G42" s="2" t="n"/>
+      <x:c r="A42" s="2"/>
+      <x:c r="B42" s="2"/>
+      <x:c r="C42" s="2"/>
+      <x:c r="D42" s="2"/>
+      <x:c r="E42" s="2"/>
+      <x:c r="F42" s="2"/>
+      <x:c r="G42" s="2"/>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
-      <x:c r="A43" s="2" t="n"/>
-      <x:c r="B43" s="2" t="n"/>
-      <x:c r="C43" s="2" t="n"/>
-      <x:c r="D43" s="2" t="n"/>
-      <x:c r="E43" s="2" t="n"/>
-      <x:c r="F43" s="2" t="n"/>
-      <x:c r="G43" s="2" t="n"/>
+      <x:c r="A43" s="2"/>
+      <x:c r="B43" s="2"/>
+      <x:c r="C43" s="2"/>
+      <x:c r="D43" s="2"/>
+      <x:c r="E43" s="2"/>
+      <x:c r="F43" s="2"/>
+      <x:c r="G43" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1293,156 +1085,134 @@
   <x:sheetPr>
     <x:tabColor rgb="FF087E87"/>
   </x:sheetPr>
-  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.75" customWidth="1"/>
-    <x:col min="2" max="2" width="26.8799991607666" customWidth="1"/>
-    <x:col min="3" max="3" width="48.130001068115234" customWidth="1"/>
-    <x:col min="4" max="4" width="15" customWidth="1"/>
-    <x:col min="5" max="5" width="17.75" customWidth="1"/>
-    <x:col min="6" max="6" width="7.5" customWidth="1"/>
-    <x:col min="7" max="7" width="10.630000114440918" customWidth="1"/>
-    <x:col min="8" max="8" width="32.5" customWidth="1"/>
-    <x:col min="9" max="9" width="28.75" customWidth="1"/>
-    <x:col min="10" max="10" width="28.75" customWidth="1"/>
-    <x:col min="11" max="11" width="28.75" customWidth="1"/>
-    <x:col min="12" max="12" width="52.5" customWidth="1"/>
-    <x:col min="13" max="13" width="16.25" customWidth="1"/>
+    <x:col min="1" max="1" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48.130001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32.5" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="52.5" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="2" t="n"/>
-      <x:c r="B1" s="2" t="n"/>
-      <x:c r="C1" s="2" t="n"/>
-      <x:c r="D1" s="2" t="n"/>
-      <x:c r="E1" s="2" t="n"/>
-      <x:c r="F1" s="2" t="n"/>
-      <x:c r="G1" s="2" t="n"/>
-      <x:c r="H1" s="2" t="n"/>
-      <x:c r="I1" s="2" t="n"/>
-      <x:c r="J1" s="2" t="n"/>
-      <x:c r="K1" s="2" t="n"/>
-      <x:c r="L1" s="2" t="n"/>
-      <x:c r="M1" s="2" t="n"/>
+      <x:c r="A1" s="2"/>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="2"/>
+      <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
+      <x:c r="M1" s="2"/>
+      <x:c r="N1" s="2"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Majucau — tarefas do backlog</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="n"/>
-      <x:c r="C2" s="2" t="n"/>
-      <x:c r="D2" s="2" t="n"/>
-      <x:c r="E2" s="2" t="n"/>
-      <x:c r="F2" s="2" t="n"/>
-      <x:c r="G2" s="2" t="n"/>
-      <x:c r="H2" s="2" t="n"/>
-      <x:c r="I2" s="2" t="n"/>
-      <x:c r="J2" s="2" t="n"/>
-      <x:c r="K2" s="2" t="n"/>
-      <x:c r="L2" s="2" t="n"/>
-      <x:c r="M2" s="2" t="n"/>
+      <x:c r="A2" s="3" t="str">
+        <x:v>Majucau — tarefas do backlog</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+      <x:c r="I2" s="2"/>
+      <x:c r="J2" s="2"/>
+      <x:c r="K2" s="2"/>
+      <x:c r="L2" s="2"/>
+      <x:c r="M2" s="2"/>
+      <x:c r="N2" s="2"/>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Detalhes de objetivo, execução, aceite e impacto: documento MAJUCAU_BACKLOG_DETALHADO_v2.md, pelo ID.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="2" t="n"/>
-      <x:c r="C3" s="2" t="n"/>
-      <x:c r="D3" s="2" t="n"/>
-      <x:c r="E3" s="2" t="n"/>
-      <x:c r="F3" s="2" t="n"/>
-      <x:c r="G3" s="2" t="n"/>
-      <x:c r="H3" s="2" t="n"/>
-      <x:c r="I3" s="2" t="n"/>
-      <x:c r="J3" s="2" t="n"/>
-      <x:c r="K3" s="2" t="n"/>
-      <x:c r="L3" s="2" t="n"/>
-      <x:c r="M3" s="2" t="n"/>
+      <x:c r="A3" s="4" t="str">
+        <x:v>Detalhes de objetivo, execução, aceite e impacto: documento MAJUCAU_BACKLOG_DETALHADO_v2.md, pelo ID.</x:v>
+      </x:c>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+      <x:c r="I3" s="2"/>
+      <x:c r="J3" s="2"/>
+      <x:c r="K3" s="2"/>
+      <x:c r="L3" s="2"/>
+      <x:c r="M3" s="2"/>
+      <x:c r="N3" s="2"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="2" t="n"/>
-      <x:c r="B4" s="2" t="n"/>
-      <x:c r="C4" s="2" t="n"/>
-      <x:c r="D4" s="2" t="n"/>
-      <x:c r="E4" s="2" t="n"/>
-      <x:c r="F4" s="2" t="n"/>
-      <x:c r="G4" s="2" t="n"/>
-      <x:c r="H4" s="2" t="n"/>
-      <x:c r="I4" s="2" t="n"/>
-      <x:c r="J4" s="2" t="n"/>
-      <x:c r="K4" s="2" t="n"/>
-      <x:c r="L4" s="2" t="n"/>
-      <x:c r="M4" s="2" t="n"/>
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+      <x:c r="I4" s="2"/>
+      <x:c r="J4" s="2"/>
+      <x:c r="K4" s="2"/>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2"/>
+      <x:c r="N4" s="2"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tarefa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Natureza</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Situação</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Peso</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Evolução</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Evidência de aceite</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Responsável sugerido</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dependências</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Decisões a acompanhar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Referências</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Peso concluído</x:t>
-        </x:is>
+      <x:c r="A5" s="8" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>Fase</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>Tarefa</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>Natureza</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>Situação</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>Peso</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>Evolução estimada</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
+        <x:v>Evidência de aceite</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>Responsável sugerido</x:v>
+      </x:c>
+      <x:c r="J5" s="8" t="str">
+        <x:v>Dependências</x:v>
+      </x:c>
+      <x:c r="K5" s="8" t="str">
+        <x:v>Decisões a acompanhar</x:v>
+      </x:c>
+      <x:c r="L5" s="8" t="str">
+        <x:v>Referências</x:v>
+      </x:c>
+      <x:c r="M5" s="8" t="str">
+        <x:v>Peso com aceite</x:v>
+      </x:c>
+      <x:c r="N5" s="8" t="str">
+        <x:v>Peso da evolução</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
@@ -1461,11 +1231,10 @@
       <x:c r="E6" s="12" t="str">
         <x:v>Concluída</x:v>
       </x:c>
-      <x:c r="F6" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G6" s="31" t="n">
-        <x:f>IF(AND(E6="Concluída",H6&lt;&gt;""),1,0)</x:f>
+      <x:c r="F6" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
@@ -1482,6 +1251,10 @@
         <x:v>Pedido do usuário; 00_Resumo; C_Conflitos; D_Lacunas; Consolidação 13/09/2026, consolidação integral; Fechamento vigente 13/09/2026, integral</x:v>
       </x:c>
       <x:c r="M6" s="10" t="n">
+        <x:f>IF(AND(E6="Concluída",H6&lt;&gt;""),F6,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6" s="10" t="n">
         <x:f>F6*G6</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -1502,11 +1275,10 @@
       <x:c r="E7" s="12" t="str">
         <x:v>Em andamento</x:v>
       </x:c>
-      <x:c r="F7" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G7" s="32" t="n">
-        <x:f>IF(AND(E7="Concluída",H7&lt;&gt;""),1,0)</x:f>
+      <x:c r="F7" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
@@ -1523,6 +1295,10 @@
         <x:v>docs/planejamento/FONTES.md; docs/source/README.md; docs/planejamento/work/source_extract; revision_v1.json; revision_v2.json</x:v>
       </x:c>
       <x:c r="M7" s="11" t="n">
+        <x:f>IF(AND(E7="Concluída",H7&lt;&gt;""),F7,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="11" t="n">
         <x:f>F7*G7</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1543,11 +1319,10 @@
       <x:c r="E8" s="12" t="str">
         <x:v>Concluída</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G8" s="31" t="n">
-        <x:f>IF(AND(E8="Concluída",H8&lt;&gt;""),1,0)</x:f>
+      <x:c r="F8" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
@@ -1557,13 +1332,15 @@
         <x:v>Arquitetura</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str"/>
-      <x:c r="K8" s="10" t="str">
-        <x:v/>
-      </x:c>
+      <x:c r="K8" s="10" t="str"/>
       <x:c r="L8" s="10" t="str">
         <x:v>GitHub REST: repos/guilhermejacyzin/majucau, branches/main, issues?state=all, pulls?state=all; git ls-remote origin; comparação origin/main..HEAD</x:v>
       </x:c>
       <x:c r="M8" s="10" t="n">
+        <x:f>IF(AND(E8="Concluída",H8&lt;&gt;""),F8,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N8" s="10" t="n">
         <x:f>F8*G8</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -1584,11 +1361,10 @@
       <x:c r="E9" s="12" t="str">
         <x:v>Concluída</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" s="32" t="n">
-        <x:f>IF(AND(E9="Concluída",H9&lt;&gt;""),1,0)</x:f>
+      <x:c r="F9" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
@@ -1605,6 +1381,10 @@
         <x:v>Todas as imagens; CEIs T11–T17</x:v>
       </x:c>
       <x:c r="M9" s="11" t="n">
+        <x:f>IF(AND(E9="Concluída",H9&lt;&gt;""),F9,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N9" s="11" t="n">
         <x:f>F9*G9</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -1625,11 +1405,10 @@
       <x:c r="E10" s="12" t="str">
         <x:v>Concluída</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" s="31" t="n">
-        <x:f>IF(AND(E10="Concluída",H10&lt;&gt;""),1,0)</x:f>
+      <x:c r="F10" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="12" t="str">
@@ -1648,6 +1427,10 @@
         <x:v>docs/source/README.md; docs/evidence/MOCAP-T1-T15-REALIGNMENT-2026-09-20.md; docs/FUNCTIONAL-DECOMPOSITION-v1.md; G0-DECISION-REGISTER.md; conferência local dos hashes em 11/10/2026</x:v>
       </x:c>
       <x:c r="M10" s="10" t="n">
+        <x:f>IF(AND(E10="Concluída",H10&lt;&gt;""),F10,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N10" s="10" t="n">
         <x:f>F10*G10</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -1668,11 +1451,10 @@
       <x:c r="E11" s="12" t="str">
         <x:v>Concluída</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G11" s="32" t="n">
-        <x:f>IF(AND(E11="Concluída",H11&lt;&gt;""),1,0)</x:f>
+      <x:c r="F11" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
@@ -1689,6 +1471,10 @@
         <x:v>C_Conflitos!A3:L3; T04; Fechamento vigente 13/09/2026, §8.6–8.8; C-01 mantida</x:v>
       </x:c>
       <x:c r="M11" s="11" t="n">
+        <x:f>IF(AND(E11="Concluída",H11&lt;&gt;""),F11,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N11" s="11" t="n">
         <x:f>F11*G11</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -1707,14 +1493,13 @@
         <x:v>Planejamento</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F12" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" s="31" t="n">
-        <x:f>IF(AND(E12="Concluída",H12&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="n">
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="H12" s="12" t="str"/>
       <x:c r="I12" s="10" t="str">
@@ -1728,8 +1513,12 @@
         <x:v>C_Conflitos!A4:L5; A_Matriz_Mestra!A32:S36; T02/T08; planilha Calculadora_Aplicacao_Lucro_Liquido_Profissional (1).xlsm enviada em 10/10/2026; fechamento de 13/09/2026, §§1–2</x:v>
       </x:c>
       <x:c r="M12" s="10" t="n">
+        <x:f>IF(AND(E12="Concluída",H12&lt;&gt;""),F12,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="10" t="n">
         <x:f>F12*G12</x:f>
-        <x:v>0</x:v>
+        <x:v>0.25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="72" customHeight="1">
@@ -1748,12 +1537,11 @@
       <x:c r="E13" s="12" t="str">
         <x:v>Em andamento</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G13" s="32" t="n">
-        <x:f>IF(AND(E13="Concluída",H13&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+      <x:c r="F13" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="n">
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H13" s="12" t="str"/>
       <x:c r="I13" s="11" t="str">
@@ -1767,8 +1555,12 @@
         <x:v>D_Lacunas; M-017..M-029; Consolidação 13/09/2026, pendências 4–6; Fechamento vigente 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M13" s="11" t="n">
+        <x:f>IF(AND(E13="Concluída",H13&lt;&gt;""),F13,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="11" t="n">
         <x:f>F13*G13</x:f>
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="72" customHeight="1">
@@ -1787,11 +1579,10 @@
       <x:c r="E14" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G14" s="31" t="n">
-        <x:f>IF(AND(E14="Concluída",H14&lt;&gt;""),1,0)</x:f>
+      <x:c r="F14" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="12" t="str"/>
@@ -1806,6 +1597,10 @@
         <x:v>T09/T10; Q_CEI_Tela_11; Consolidação 13/09/2026, §3; Fechamento vigente 13/09/2026, §§3–4</x:v>
       </x:c>
       <x:c r="M14" s="10" t="n">
+        <x:f>IF(AND(E14="Concluída",H14&lt;&gt;""),F14,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="10" t="n">
         <x:f>F14*G14</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1826,11 +1621,10 @@
       <x:c r="E15" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G15" s="32" t="n">
-        <x:f>IF(AND(E15="Concluída",H15&lt;&gt;""),1,0)</x:f>
+      <x:c r="F15" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="12" t="str"/>
@@ -1845,6 +1639,10 @@
         <x:v>R_CEI_Tela_12; T12; M-045..M-049; Consolidação 13/09/2026, pendência 9; Fechamento vigente 13/09/2026, §4</x:v>
       </x:c>
       <x:c r="M15" s="11" t="n">
+        <x:f>IF(AND(E15="Concluída",H15&lt;&gt;""),F15,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="11" t="n">
         <x:f>F15*G15</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1865,11 +1663,10 @@
       <x:c r="E16" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G16" s="31" t="n">
-        <x:f>IF(AND(E16="Concluída",H16&lt;&gt;""),1,0)</x:f>
+      <x:c r="F16" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="12" t="str"/>
@@ -1884,6 +1681,10 @@
         <x:v>H_Contrato_Dados; U_CEI_Tela_15; Consolidação 13/09/2026, §§1–2,10–12; Fechamento vigente 13/09/2026, §8</x:v>
       </x:c>
       <x:c r="M16" s="10" t="n">
+        <x:f>IF(AND(E16="Concluída",H16&lt;&gt;""),F16,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="10" t="n">
         <x:f>F16*G16</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1904,11 +1705,10 @@
       <x:c r="E17" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G17" s="32" t="n">
-        <x:f>IF(AND(E17="Concluída",H17&lt;&gt;""),1,0)</x:f>
+      <x:c r="F17" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="12" t="str"/>
@@ -1923,6 +1723,10 @@
         <x:v>Q_CEI_Tela_11; H_Contrato_Dados!A21:H22; Consolidação 13/09/2026, pendência 10; Fechamento vigente 13/09/2026, §3.4</x:v>
       </x:c>
       <x:c r="M17" s="11" t="n">
+        <x:f>IF(AND(E17="Concluída",H17&lt;&gt;""),F17,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="11" t="n">
         <x:f>F17*G17</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1941,14 +1745,13 @@
         <x:v>Planejamento</x:v>
       </x:c>
       <x:c r="E18" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F18" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G18" s="31" t="n">
-        <x:f>IF(AND(E18="Concluída",H18&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="n">
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="H18" s="12" t="str"/>
       <x:c r="I18" s="10" t="str">
@@ -1962,8 +1765,12 @@
         <x:v>S/T/U CEIs; T02–T07; T13–T15; Fechamento vigente 13/09/2026, §§5–6</x:v>
       </x:c>
       <x:c r="M18" s="10" t="n">
+        <x:f>IF(AND(E18="Concluída",H18&lt;&gt;""),F18,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="10" t="n">
         <x:f>F18*G18</x:f>
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="72" customHeight="1">
@@ -1980,14 +1787,13 @@
         <x:v>Planejamento</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F19" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G19" s="32" t="n">
-        <x:f>IF(AND(E19="Concluída",H19&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="n">
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="H19" s="12" t="str"/>
       <x:c r="I19" s="11" t="str">
@@ -2001,8 +1807,12 @@
         <x:v>W/Y CEIs; H_Contrato_Dados!A34:H39; Fechamento vigente 13/09/2026, §6</x:v>
       </x:c>
       <x:c r="M19" s="11" t="n">
+        <x:f>IF(AND(E19="Concluída",H19&lt;&gt;""),F19,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="11" t="n">
         <x:f>F19*G19</x:f>
-        <x:v>0</x:v>
+        <x:v>0.15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="72" customHeight="1">
@@ -2019,14 +1829,13 @@
         <x:v>Planejamento</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F20" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G20" s="31" t="n">
-        <x:f>IF(AND(E20="Concluída",H20&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="n">
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="H20" s="12" t="str"/>
       <x:c r="I20" s="10" t="str">
@@ -2040,8 +1849,12 @@
         <x:v>Pedido: hospedagem local; Fechamento vigente 13/09/2026, §7</x:v>
       </x:c>
       <x:c r="M20" s="10" t="n">
+        <x:f>IF(AND(E20="Concluída",H20&lt;&gt;""),F20,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="10" t="n">
         <x:f>F20*G20</x:f>
-        <x:v>0</x:v>
+        <x:v>0.15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="72" customHeight="1">
@@ -2060,11 +1873,10 @@
       <x:c r="E21" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F21" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G21" s="32" t="n">
-        <x:f>IF(AND(E21="Concluída",H21&lt;&gt;""),1,0)</x:f>
+      <x:c r="F21" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="12" t="str"/>
@@ -2081,6 +1893,10 @@
         <x:v>Pedido do usuário; G_Ordem; Fechamento vigente 13/09/2026, §7</x:v>
       </x:c>
       <x:c r="M21" s="11" t="n">
+        <x:f>IF(AND(E21="Concluída",H21&lt;&gt;""),F21,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N21" s="11" t="n">
         <x:f>F21*G21</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2101,11 +1917,10 @@
       <x:c r="E22" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F22" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G22" s="31" t="n">
-        <x:f>IF(AND(E22="Concluída",H22&lt;&gt;""),1,0)</x:f>
+      <x:c r="F22" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="12" t="str"/>
@@ -2120,6 +1935,10 @@
         <x:v>A_Matriz_Mestra; B_Intersecoes; H_Contrato_Dados; Consolidação 13/09/2026, §§6,10–12; Fechamento vigente 13/09/2026, §§1–4</x:v>
       </x:c>
       <x:c r="M22" s="10" t="n">
+        <x:f>IF(AND(E22="Concluída",H22&lt;&gt;""),F22,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N22" s="10" t="n">
         <x:f>F22*G22</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2140,11 +1959,10 @@
       <x:c r="E23" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F23" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G23" s="32" t="n">
-        <x:f>IF(AND(E23="Concluída",H23&lt;&gt;""),1,0)</x:f>
+      <x:c r="F23" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="12" t="str"/>
@@ -2159,6 +1977,10 @@
         <x:v>Stack definida pelo usuário</x:v>
       </x:c>
       <x:c r="M23" s="11" t="n">
+        <x:f>IF(AND(E23="Concluída",H23&lt;&gt;""),F23,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N23" s="11" t="n">
         <x:f>F23*G23</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2179,11 +2001,10 @@
       <x:c r="E24" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F24" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G24" s="31" t="n">
-        <x:f>IF(AND(E24="Concluída",H24&lt;&gt;""),1,0)</x:f>
+      <x:c r="F24" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="12" t="str"/>
@@ -2198,6 +2019,10 @@
         <x:v>H_Contrato_Dados; proposta técnica</x:v>
       </x:c>
       <x:c r="M24" s="10" t="n">
+        <x:f>IF(AND(E24="Concluída",H24&lt;&gt;""),F24,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N24" s="10" t="n">
         <x:f>F24*G24</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2218,11 +2043,10 @@
       <x:c r="E25" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F25" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G25" s="32" t="n">
-        <x:f>IF(AND(E25="Concluída",H25&lt;&gt;""),1,0)</x:f>
+      <x:c r="F25" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="12" t="str"/>
@@ -2239,6 +2063,10 @@
         <x:v>H_Contrato_Dados; todos CEIs; Fechamento vigente 13/09/2026, §1</x:v>
       </x:c>
       <x:c r="M25" s="11" t="n">
+        <x:f>IF(AND(E25="Concluída",H25&lt;&gt;""),F25,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N25" s="11" t="n">
         <x:f>F25*G25</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2259,11 +2087,10 @@
       <x:c r="E26" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F26" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G26" s="31" t="n">
-        <x:f>IF(AND(E26="Concluída",H26&lt;&gt;""),1,0)</x:f>
+      <x:c r="F26" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="12" t="str"/>
@@ -2280,6 +2107,10 @@
         <x:v>M-002,M-037,M-038; H_Contrato_Dados; Fechamento vigente 13/09/2026, §§4.3,8.7–8.8</x:v>
       </x:c>
       <x:c r="M26" s="10" t="n">
+        <x:f>IF(AND(E26="Concluída",H26&lt;&gt;""),F26,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="10" t="n">
         <x:f>F26*G26</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2300,11 +2131,10 @@
       <x:c r="E27" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F27" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G27" s="32" t="n">
-        <x:f>IF(AND(E27="Concluída",H27&lt;&gt;""),1,0)</x:f>
+      <x:c r="F27" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="12" t="str"/>
@@ -2321,6 +2151,10 @@
         <x:v>Todas as imagens; M-039,M-050; Fechamento vigente 13/09/2026, §5</x:v>
       </x:c>
       <x:c r="M27" s="11" t="n">
+        <x:f>IF(AND(E27="Concluída",H27&lt;&gt;""),F27,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="11" t="n">
         <x:f>F27*G27</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2341,11 +2175,10 @@
       <x:c r="E28" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F28" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G28" s="31" t="n">
-        <x:f>IF(AND(E28="Concluída",H28&lt;&gt;""),1,0)</x:f>
+      <x:c r="F28" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="12" t="str"/>
@@ -2362,6 +2195,10 @@
         <x:v>Todas as imagens; gaps UX; Fechamento vigente 13/09/2026, §5</x:v>
       </x:c>
       <x:c r="M28" s="10" t="n">
+        <x:f>IF(AND(E28="Concluída",H28&lt;&gt;""),F28,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="10" t="n">
         <x:f>F28*G28</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2382,11 +2219,10 @@
       <x:c r="E29" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F29" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" s="32" t="n">
-        <x:f>IF(AND(E29="Concluída",H29&lt;&gt;""),1,0)</x:f>
+      <x:c r="F29" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="12" t="str"/>
@@ -2401,6 +2237,10 @@
         <x:v>Sugestão permitida pelo usuário; proposta técnica</x:v>
       </x:c>
       <x:c r="M29" s="11" t="n">
+        <x:f>IF(AND(E29="Concluída",H29&lt;&gt;""),F29,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="11" t="n">
         <x:f>F29*G29</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2421,11 +2261,10 @@
       <x:c r="E30" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F30" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G30" s="31" t="n">
-        <x:f>IF(AND(E30="Concluída",H30&lt;&gt;""),1,0)</x:f>
+      <x:c r="F30" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str"/>
@@ -2442,6 +2281,10 @@
         <x:v>M-058; Y_CEI_Tela_17; Consolidação 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M30" s="10" t="n">
+        <x:f>IF(AND(E30="Concluída",H30&lt;&gt;""),F30,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N30" s="10" t="n">
         <x:f>F30*G30</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2460,14 +2303,13 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E31" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F31" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G31" s="32" t="n">
-        <x:f>IF(AND(E31="Concluída",H31&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F31" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="H31" s="12" t="str"/>
       <x:c r="I31" s="11" t="str">
@@ -2481,8 +2323,12 @@
         <x:v>GitHub vazio; BK arquitetura</x:v>
       </x:c>
       <x:c r="M31" s="11" t="n">
+        <x:f>IF(AND(E31="Concluída",H31&lt;&gt;""),F31,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N31" s="11" t="n">
         <x:f>F31*G31</x:f>
-        <x:v>0</x:v>
+        <x:v>0.7</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="72" customHeight="1">
@@ -2501,11 +2347,10 @@
       <x:c r="E32" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F32" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G32" s="31" t="n">
-        <x:f>IF(AND(E32="Concluída",H32&lt;&gt;""),1,0)</x:f>
+      <x:c r="F32" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="12" t="str"/>
@@ -2520,6 +2365,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M32" s="10" t="n">
+        <x:f>IF(AND(E32="Concluída",H32&lt;&gt;""),F32,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" s="10" t="n">
         <x:f>F32*G32</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2540,11 +2389,10 @@
       <x:c r="E33" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F33" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G33" s="32" t="n">
-        <x:f>IF(AND(E33="Concluída",H33&lt;&gt;""),1,0)</x:f>
+      <x:c r="F33" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="12" t="str"/>
@@ -2559,6 +2407,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M33" s="11" t="n">
+        <x:f>IF(AND(E33="Concluída",H33&lt;&gt;""),F33,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N33" s="11" t="n">
         <x:f>F33*G33</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2579,11 +2431,10 @@
       <x:c r="E34" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F34" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G34" s="31" t="n">
-        <x:f>IF(AND(E34="Concluída",H34&lt;&gt;""),1,0)</x:f>
+      <x:c r="F34" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="12" t="str"/>
@@ -2598,6 +2449,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M34" s="10" t="n">
+        <x:f>IF(AND(E34="Concluída",H34&lt;&gt;""),F34,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" s="10" t="n">
         <x:f>F34*G34</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2618,11 +2473,10 @@
       <x:c r="E35" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F35" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G35" s="32" t="n">
-        <x:f>IF(AND(E35="Concluída",H35&lt;&gt;""),1,0)</x:f>
+      <x:c r="F35" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="12" t="str"/>
@@ -2637,6 +2491,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M35" s="11" t="n">
+        <x:f>IF(AND(E35="Concluída",H35&lt;&gt;""),F35,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" s="11" t="n">
         <x:f>F35*G35</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2655,16 +2513,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E36" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F36" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G36" s="31" t="n">
-        <x:f>IF(AND(E36="Concluída",H36&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="12" t="str"/>
+        <x:v>Concluída</x:v>
+      </x:c>
+      <x:c r="F36" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="str">
+        <x:v>A CI 38115370056 comprovou o fluxo de sucesso das verificações, build e publicação condicionada; evidência e escopo estão descritos nesta tarefa.</x:v>
+      </x:c>
       <x:c r="I36" s="10" t="str">
         <x:v>Engenharia + Infraestrutura</x:v>
       </x:c>
@@ -2676,8 +2535,12 @@
         <x:v>Repositório público; recomendação GitHub Actions</x:v>
       </x:c>
       <x:c r="M36" s="10" t="n">
+        <x:f>IF(AND(E36="Concluída",H36&lt;&gt;""),F36,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N36" s="10" t="n">
         <x:f>F36*G36</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="72" customHeight="1">
@@ -2694,14 +2557,13 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E37" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F37" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G37" s="32" t="n">
-        <x:f>IF(AND(E37="Concluída",H37&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F37" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="n">
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H37" s="12" t="str"/>
       <x:c r="I37" s="11" t="str">
@@ -2715,8 +2577,12 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M37" s="11" t="n">
+        <x:f>IF(AND(E37="Concluída",H37&lt;&gt;""),F37,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" s="11" t="n">
         <x:f>F37*G37</x:f>
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="72" customHeight="1">
@@ -2735,11 +2601,10 @@
       <x:c r="E38" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F38" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G38" s="31" t="n">
-        <x:f>IF(AND(E38="Concluída",H38&lt;&gt;""),1,0)</x:f>
+      <x:c r="F38" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G38" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="12" t="str"/>
@@ -2756,6 +2621,10 @@
         <x:v>L-26; Y_CEI_Tela_17</x:v>
       </x:c>
       <x:c r="M38" s="10" t="n">
+        <x:f>IF(AND(E38="Concluída",H38&lt;&gt;""),F38,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" s="10" t="n">
         <x:f>F38*G38</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2776,11 +2645,10 @@
       <x:c r="E39" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F39" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G39" s="32" t="n">
-        <x:f>IF(AND(E39="Concluída",H39&lt;&gt;""),1,0)</x:f>
+      <x:c r="F39" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="12" t="str"/>
@@ -2797,6 +2665,10 @@
         <x:v>M-057,M-058; H_Contrato_Dados!A38:H38; Fechamento vigente 13/09/2026, §6</x:v>
       </x:c>
       <x:c r="M39" s="11" t="n">
+        <x:f>IF(AND(E39="Concluída",H39&lt;&gt;""),F39,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="11" t="n">
         <x:f>F39*G39</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2817,11 +2689,10 @@
       <x:c r="E40" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F40" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G40" s="31" t="n">
-        <x:f>IF(AND(E40="Concluída",H40&lt;&gt;""),1,0)</x:f>
+      <x:c r="F40" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G40" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="12" t="str"/>
@@ -2838,6 +2709,10 @@
         <x:v>H_Contrato_Dados!A39:H39; Fechamento vigente 13/09/2026, §6.8</x:v>
       </x:c>
       <x:c r="M40" s="10" t="n">
+        <x:f>IF(AND(E40="Concluída",H40&lt;&gt;""),F40,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="10" t="n">
         <x:f>F40*G40</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2858,11 +2733,10 @@
       <x:c r="E41" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F41" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G41" s="32" t="n">
-        <x:f>IF(AND(E41="Concluída",H41&lt;&gt;""),1,0)</x:f>
+      <x:c r="F41" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H41" s="12" t="str"/>
@@ -2879,6 +2753,10 @@
         <x:v>T17; Y_CEI_Tela_17; T-CEI17-01..08</x:v>
       </x:c>
       <x:c r="M41" s="11" t="n">
+        <x:f>IF(AND(E41="Concluída",H41&lt;&gt;""),F41,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N41" s="11" t="n">
         <x:f>F41*G41</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2899,11 +2777,10 @@
       <x:c r="E42" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F42" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G42" s="31" t="n">
-        <x:f>IF(AND(E42="Concluída",H42&lt;&gt;""),1,0)</x:f>
+      <x:c r="F42" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="12" t="str"/>
@@ -2920,6 +2797,10 @@
         <x:v>M-056; H_Contrato_Dados!A34:H35; Fechamento vigente 13/09/2026, §6.3–6.7</x:v>
       </x:c>
       <x:c r="M42" s="10" t="n">
+        <x:f>IF(AND(E42="Concluída",H42&lt;&gt;""),F42,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N42" s="10" t="n">
         <x:f>F42*G42</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2940,11 +2821,10 @@
       <x:c r="E43" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F43" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G43" s="32" t="n">
-        <x:f>IF(AND(E43="Concluída",H43&lt;&gt;""),1,0)</x:f>
+      <x:c r="F43" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G43" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="12" t="str"/>
@@ -2961,6 +2841,10 @@
         <x:v>T16; W_CEI_Tela_16; T-CEI16-01..08; Consolidação 13/09/2026, §§1,4–5; Fechamento vigente 13/09/2026, §6</x:v>
       </x:c>
       <x:c r="M43" s="11" t="n">
+        <x:f>IF(AND(E43="Concluída",H43&lt;&gt;""),F43,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N43" s="11" t="n">
         <x:f>F43*G43</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2981,11 +2865,10 @@
       <x:c r="E44" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F44" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G44" s="31" t="n">
-        <x:f>IF(AND(E44="Concluída",H44&lt;&gt;""),1,0)</x:f>
+      <x:c r="F44" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="12" t="str"/>
@@ -3002,6 +2885,10 @@
         <x:v>M-037; H_Contrato_Dados!A3:H3; Consolidação 13/09/2026, §2; Fechamento vigente 13/09/2026, §6.6–6.8</x:v>
       </x:c>
       <x:c r="M44" s="10" t="n">
+        <x:f>IF(AND(E44="Concluída",H44&lt;&gt;""),F44,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N44" s="10" t="n">
         <x:f>F44*G44</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3022,11 +2909,10 @@
       <x:c r="E45" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F45" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G45" s="32" t="n">
-        <x:f>IF(AND(E45="Concluída",H45&lt;&gt;""),1,0)</x:f>
+      <x:c r="F45" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G45" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H45" s="12" t="str"/>
@@ -3043,6 +2929,10 @@
         <x:v>U_CEI_Tela_15; Fechamento vigente 13/09/2026, §8.11</x:v>
       </x:c>
       <x:c r="M45" s="11" t="n">
+        <x:f>IF(AND(E45="Concluída",H45&lt;&gt;""),F45,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N45" s="11" t="n">
         <x:f>F45*G45</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3063,11 +2953,10 @@
       <x:c r="E46" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F46" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G46" s="31" t="n">
-        <x:f>IF(AND(E46="Concluída",H46&lt;&gt;""),1,0)</x:f>
+      <x:c r="F46" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H46" s="12" t="str"/>
@@ -3084,6 +2973,10 @@
         <x:v>Bling documentação oficial; H_Contrato_Dados; Consolidação 13/09/2026, §§3–9; pendências 1–8; Fechamento vigente 13/09/2026, §§2,8</x:v>
       </x:c>
       <x:c r="M46" s="10" t="n">
+        <x:f>IF(AND(E46="Concluída",H46&lt;&gt;""),F46,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N46" s="10" t="n">
         <x:f>F46*G46</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3102,14 +2995,13 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E47" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F47" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G47" s="32" t="n">
-        <x:f>IF(AND(E47="Concluída",H47&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F47" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47" s="17" t="n">
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str"/>
       <x:c r="I47" s="11" t="str">
@@ -3125,8 +3017,12 @@
         <x:v>M-003,M-035; documentação Bling; Consolidação 13/09/2026, §§4,8–9; Fechamento vigente 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M47" s="11" t="n">
+        <x:f>IF(AND(E47="Concluída",H47&lt;&gt;""),F47,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N47" s="11" t="n">
         <x:f>F47*G47</x:f>
-        <x:v>0</x:v>
+        <x:v>0.55</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="72" customHeight="1">
@@ -3145,11 +3041,10 @@
       <x:c r="E48" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F48" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G48" s="31" t="n">
-        <x:f>IF(AND(E48="Concluída",H48&lt;&gt;""),1,0)</x:f>
+      <x:c r="F48" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H48" s="12" t="str"/>
@@ -3166,6 +3061,10 @@
         <x:v>M-009,M-010; L-11,L-12; Consolidação 13/09/2026, §§1–2</x:v>
       </x:c>
       <x:c r="M48" s="10" t="n">
+        <x:f>IF(AND(E48="Concluída",H48&lt;&gt;""),F48,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N48" s="10" t="n">
         <x:f>F48*G48</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3186,11 +3085,10 @@
       <x:c r="E49" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F49" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G49" s="32" t="n">
-        <x:f>IF(AND(E49="Concluída",H49&lt;&gt;""),1,0)</x:f>
+      <x:c r="F49" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G49" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="12" t="str"/>
@@ -3205,6 +3103,10 @@
         <x:v>H_Contrato_Dados; T-FILE-*; Consolidação 13/09/2026, §§1–2,4</x:v>
       </x:c>
       <x:c r="M49" s="11" t="n">
+        <x:f>IF(AND(E49="Concluída",H49&lt;&gt;""),F49,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N49" s="11" t="n">
         <x:f>F49*G49</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3225,11 +3127,10 @@
       <x:c r="E50" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F50" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G50" s="31" t="n">
-        <x:f>IF(AND(E50="Concluída",H50&lt;&gt;""),1,0)</x:f>
+      <x:c r="F50" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G50" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="12" t="str"/>
@@ -3246,6 +3147,10 @@
         <x:v>M-038; T-IDEMP-*; Consolidação 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M50" s="10" t="n">
+        <x:f>IF(AND(E50="Concluída",H50&lt;&gt;""),F50,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N50" s="10" t="n">
         <x:f>F50*G50</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3266,11 +3171,10 @@
       <x:c r="E51" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F51" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G51" s="32" t="n">
-        <x:f>IF(AND(E51="Concluída",H51&lt;&gt;""),1,0)</x:f>
+      <x:c r="F51" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G51" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="12" t="str"/>
@@ -3285,6 +3189,10 @@
         <x:v>M-003; H_Contrato_Dados!A4:H4</x:v>
       </x:c>
       <x:c r="M51" s="11" t="n">
+        <x:f>IF(AND(E51="Concluída",H51&lt;&gt;""),F51,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N51" s="11" t="n">
         <x:f>F51*G51</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3305,11 +3213,10 @@
       <x:c r="E52" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F52" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G52" s="31" t="n">
-        <x:f>IF(AND(E52="Concluída",H52&lt;&gt;""),1,0)</x:f>
+      <x:c r="F52" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H52" s="12" t="str"/>
@@ -3326,6 +3233,10 @@
         <x:v>M-004,M-005,M-011,M-012; H_Contrato_Dados!A5:H6; Consolidação 13/09/2026, §10; Fechamento vigente 13/09/2026, §8.2,8.5,8.11</x:v>
       </x:c>
       <x:c r="M52" s="10" t="n">
+        <x:f>IF(AND(E52="Concluída",H52&lt;&gt;""),F52,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N52" s="10" t="n">
         <x:f>F52*G52</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3346,11 +3257,10 @@
       <x:c r="E53" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F53" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G53" s="32" t="n">
-        <x:f>IF(AND(E53="Concluída",H53&lt;&gt;""),1,0)</x:f>
+      <x:c r="F53" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G53" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="12" t="str"/>
@@ -3367,6 +3277,10 @@
         <x:v>M-006,M-007; T04; Consolidação 13/09/2026, §§8–10</x:v>
       </x:c>
       <x:c r="M53" s="11" t="n">
+        <x:f>IF(AND(E53="Concluída",H53&lt;&gt;""),F53,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N53" s="11" t="n">
         <x:f>F53*G53</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3387,11 +3301,10 @@
       <x:c r="E54" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F54" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G54" s="31" t="n">
-        <x:f>IF(AND(E54="Concluída",H54&lt;&gt;""),1,0)</x:f>
+      <x:c r="F54" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G54" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="12" t="str"/>
@@ -3408,6 +3321,10 @@
         <x:v>M-035; H_Contrato_Dados!A11:H14,A19:H20; Consolidação 13/09/2026, §3; pendência 7</x:v>
       </x:c>
       <x:c r="M54" s="10" t="n">
+        <x:f>IF(AND(E54="Concluída",H54&lt;&gt;""),F54,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N54" s="10" t="n">
         <x:f>F54*G54</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3428,11 +3345,10 @@
       <x:c r="E55" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F55" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G55" s="32" t="n">
-        <x:f>IF(AND(E55="Concluída",H55&lt;&gt;""),1,0)</x:f>
+      <x:c r="F55" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G55" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H55" s="12" t="str"/>
@@ -3449,6 +3365,10 @@
         <x:v>M-013..M-016; H_Contrato_Dados!A7:H9; Consolidação 13/09/2026, §12</x:v>
       </x:c>
       <x:c r="M55" s="11" t="n">
+        <x:f>IF(AND(E55="Concluída",H55&lt;&gt;""),F55,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N55" s="11" t="n">
         <x:f>F55*G55</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3469,11 +3389,10 @@
       <x:c r="E56" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F56" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G56" s="31" t="n">
-        <x:f>IF(AND(E56="Concluída",H56&lt;&gt;""),1,0)</x:f>
+      <x:c r="F56" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="12" t="str"/>
@@ -3490,6 +3409,10 @@
         <x:v>M-024..M-029,M-033; T15; Consolidação 13/09/2026, §11</x:v>
       </x:c>
       <x:c r="M56" s="10" t="n">
+        <x:f>IF(AND(E56="Concluída",H56&lt;&gt;""),F56,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N56" s="10" t="n">
         <x:f>F56*G56</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3510,11 +3433,10 @@
       <x:c r="E57" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F57" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G57" s="32" t="n">
-        <x:f>IF(AND(E57="Concluída",H57&lt;&gt;""),1,0)</x:f>
+      <x:c r="F57" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G57" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="12" t="str"/>
@@ -3531,6 +3453,10 @@
         <x:v>L-24; U_CEI_Tela_15; Consolidação 13/09/2026, §10; Fechamento vigente 13/09/2026, §8.11</x:v>
       </x:c>
       <x:c r="M57" s="11" t="n">
+        <x:f>IF(AND(E57="Concluída",H57&lt;&gt;""),F57,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N57" s="11" t="n">
         <x:f>F57*G57</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3551,11 +3477,10 @@
       <x:c r="E58" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F58" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G58" s="31" t="n">
-        <x:f>IF(AND(E58="Concluída",H58&lt;&gt;""),1,0)</x:f>
+      <x:c r="F58" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G58" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H58" s="12" t="str"/>
@@ -3572,6 +3497,10 @@
         <x:v>T15; U_CEI_Tela_15; T-CEI15-01..08; Consolidação 13/09/2026, §§1–2</x:v>
       </x:c>
       <x:c r="M58" s="10" t="n">
+        <x:f>IF(AND(E58="Concluída",H58&lt;&gt;""),F58,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N58" s="10" t="n">
         <x:f>F58*G58</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3592,11 +3521,10 @@
       <x:c r="E59" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F59" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G59" s="32" t="n">
-        <x:f>IF(AND(E59="Concluída",H59&lt;&gt;""),1,0)</x:f>
+      <x:c r="F59" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G59" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="12" t="str"/>
@@ -3613,6 +3541,10 @@
         <x:v>M-008; T03/T05; Consolidação 13/09/2026, §10; pendência 8; Fechamento vigente 13/09/2026, §8.6–8.8,8.11</x:v>
       </x:c>
       <x:c r="M59" s="11" t="n">
+        <x:f>IF(AND(E59="Concluída",H59&lt;&gt;""),F59,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N59" s="11" t="n">
         <x:f>F59*G59</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3633,11 +3565,10 @@
       <x:c r="E60" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F60" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G60" s="31" t="n">
-        <x:f>IF(AND(E60="Concluída",H60&lt;&gt;""),1,0)</x:f>
+      <x:c r="F60" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G60" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H60" s="12" t="str"/>
@@ -3654,6 +3585,10 @@
         <x:v>L-23; T05/T13; Fechamento vigente 13/09/2026, §8.11</x:v>
       </x:c>
       <x:c r="M60" s="10" t="n">
+        <x:f>IF(AND(E60="Concluída",H60&lt;&gt;""),F60,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N60" s="10" t="n">
         <x:f>F60*G60</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3674,11 +3609,10 @@
       <x:c r="E61" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F61" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G61" s="32" t="n">
-        <x:f>IF(AND(E61="Concluída",H61&lt;&gt;""),1,0)</x:f>
+      <x:c r="F61" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G61" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="12" t="str"/>
@@ -3693,6 +3627,10 @@
         <x:v>T05; T-RECON-*</x:v>
       </x:c>
       <x:c r="M61" s="11" t="n">
+        <x:f>IF(AND(E61="Concluída",H61&lt;&gt;""),F61,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N61" s="11" t="n">
         <x:f>F61*G61</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3713,11 +3651,10 @@
       <x:c r="E62" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F62" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G62" s="31" t="n">
-        <x:f>IF(AND(E62="Concluída",H62&lt;&gt;""),1,0)</x:f>
+      <x:c r="F62" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G62" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H62" s="12" t="str"/>
@@ -3734,6 +3671,10 @@
         <x:v>T03; M-004,M-005; Consolidação 13/09/2026, §10; Fechamento vigente 13/09/2026, §8.5–8.11</x:v>
       </x:c>
       <x:c r="M62" s="10" t="n">
+        <x:f>IF(AND(E62="Concluída",H62&lt;&gt;""),F62,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N62" s="10" t="n">
         <x:f>F62*G62</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3754,11 +3695,10 @@
       <x:c r="E63" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F63" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G63" s="32" t="n">
-        <x:f>IF(AND(E63="Concluída",H63&lt;&gt;""),1,0)</x:f>
+      <x:c r="F63" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G63" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="12" t="str"/>
@@ -3773,6 +3713,10 @@
         <x:v>T03</x:v>
       </x:c>
       <x:c r="M63" s="11" t="n">
+        <x:f>IF(AND(E63="Concluída",H63&lt;&gt;""),F63,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N63" s="11" t="n">
         <x:f>F63*G63</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3793,11 +3737,10 @@
       <x:c r="E64" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F64" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G64" s="31" t="n">
-        <x:f>IF(AND(E64="Concluída",H64&lt;&gt;""),1,0)</x:f>
+      <x:c r="F64" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="12" t="str"/>
@@ -3812,6 +3755,10 @@
         <x:v>T04; C-01</x:v>
       </x:c>
       <x:c r="M64" s="10" t="n">
+        <x:f>IF(AND(E64="Concluída",H64&lt;&gt;""),F64,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N64" s="10" t="n">
         <x:f>F64*G64</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3832,11 +3779,10 @@
       <x:c r="E65" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F65" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G65" s="32" t="n">
-        <x:f>IF(AND(E65="Concluída",H65&lt;&gt;""),1,0)</x:f>
+      <x:c r="F65" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G65" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="12" t="str"/>
@@ -3851,6 +3797,10 @@
         <x:v>T04</x:v>
       </x:c>
       <x:c r="M65" s="11" t="n">
+        <x:f>IF(AND(E65="Concluída",H65&lt;&gt;""),F65,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N65" s="11" t="n">
         <x:f>F65*G65</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3871,11 +3821,10 @@
       <x:c r="E66" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F66" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G66" s="31" t="n">
-        <x:f>IF(AND(E66="Concluída",H66&lt;&gt;""),1,0)</x:f>
+      <x:c r="F66" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G66" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="12" t="str"/>
@@ -3892,6 +3841,10 @@
         <x:v>T02; M-002; C-02; L-07; Consolidação 13/09/2026, §§8–10; Fechamento vigente 13/09/2026, §§1,8.5–8.11</x:v>
       </x:c>
       <x:c r="M66" s="10" t="n">
+        <x:f>IF(AND(E66="Concluída",H66&lt;&gt;""),F66,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N66" s="10" t="n">
         <x:f>F66*G66</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3912,11 +3865,10 @@
       <x:c r="E67" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F67" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G67" s="32" t="n">
-        <x:f>IF(AND(E67="Concluída",H67&lt;&gt;""),1,0)</x:f>
+      <x:c r="F67" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H67" s="12" t="str"/>
@@ -3933,6 +3885,10 @@
         <x:v>T02/T08; C-02,L-07; Fechamento vigente 13/09/2026, §1</x:v>
       </x:c>
       <x:c r="M67" s="11" t="n">
+        <x:f>IF(AND(E67="Concluída",H67&lt;&gt;""),F67,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N67" s="11" t="n">
         <x:f>F67*G67</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3953,11 +3909,10 @@
       <x:c r="E68" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F68" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G68" s="31" t="n">
-        <x:f>IF(AND(E68="Concluída",H68&lt;&gt;""),1,0)</x:f>
+      <x:c r="F68" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G68" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="12" t="str"/>
@@ -3972,6 +3927,10 @@
         <x:v>T02; Consolidação 13/09/2026, §§8–10</x:v>
       </x:c>
       <x:c r="M68" s="10" t="n">
+        <x:f>IF(AND(E68="Concluída",H68&lt;&gt;""),F68,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N68" s="10" t="n">
         <x:f>F68*G68</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3992,11 +3951,10 @@
       <x:c r="E69" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F69" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G69" s="32" t="n">
-        <x:f>IF(AND(E69="Concluída",H69&lt;&gt;""),1,0)</x:f>
+      <x:c r="F69" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G69" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="12" t="str"/>
@@ -4013,6 +3971,10 @@
         <x:v>M-019,M-020; L-03; Consolidação 13/09/2026, pendência 5</x:v>
       </x:c>
       <x:c r="M69" s="11" t="n">
+        <x:f>IF(AND(E69="Concluída",H69&lt;&gt;""),F69,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N69" s="11" t="n">
         <x:f>F69*G69</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4033,11 +3995,10 @@
       <x:c r="E70" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F70" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G70" s="31" t="n">
-        <x:f>IF(AND(E70="Concluída",H70&lt;&gt;""),1,0)</x:f>
+      <x:c r="F70" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G70" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="12" t="str"/>
@@ -4054,6 +4015,10 @@
         <x:v>M-017,M-018,M-029; H_Contrato_Dados!A18:H18; Consolidação 13/09/2026, pendência 6; §12; Fechamento vigente 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M70" s="10" t="n">
+        <x:f>IF(AND(E70="Concluída",H70&lt;&gt;""),F70,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N70" s="10" t="n">
         <x:f>F70*G70</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4074,11 +4039,10 @@
       <x:c r="E71" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F71" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G71" s="32" t="n">
-        <x:f>IF(AND(E71="Concluída",H71&lt;&gt;""),1,0)</x:f>
+      <x:c r="F71" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G71" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H71" s="12" t="str"/>
@@ -4095,6 +4059,10 @@
         <x:v>M-024..M-026; L-04,L-14; Consolidação 13/09/2026, §11; Fechamento vigente 13/09/2026, §§2,8.14</x:v>
       </x:c>
       <x:c r="M71" s="11" t="n">
+        <x:f>IF(AND(E71="Concluída",H71&lt;&gt;""),F71,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N71" s="11" t="n">
         <x:f>F71*G71</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4115,11 +4083,10 @@
       <x:c r="E72" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F72" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G72" s="31" t="n">
-        <x:f>IF(AND(E72="Concluída",H72&lt;&gt;""),1,0)</x:f>
+      <x:c r="F72" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G72" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H72" s="12" t="str"/>
@@ -4136,6 +4103,10 @@
         <x:v>T06; M-017..M-029; Fechamento vigente 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M72" s="10" t="n">
+        <x:f>IF(AND(E72="Concluída",H72&lt;&gt;""),F72,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N72" s="10" t="n">
         <x:f>F72*G72</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4154,14 +4125,13 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E73" s="12" t="str">
-        <x:v>Não iniciada</x:v>
-      </x:c>
-      <x:c r="F73" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G73" s="32" t="n">
-        <x:f>IF(AND(E73="Concluída",H73&lt;&gt;""),1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F73" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G73" s="17" t="n">
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H73" s="12" t="str"/>
       <x:c r="I73" s="11" t="str">
@@ -4177,8 +4147,12 @@
         <x:v>T06; Fechamento vigente 13/09/2026, §§2,5</x:v>
       </x:c>
       <x:c r="M73" s="11" t="n">
+        <x:f>IF(AND(E73="Concluída",H73&lt;&gt;""),F73,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N73" s="11" t="n">
         <x:f>F73*G73</x:f>
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="72" customHeight="1">
@@ -4197,11 +4171,10 @@
       <x:c r="E74" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F74" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G74" s="31" t="n">
-        <x:f>IF(AND(E74="Concluída",H74&lt;&gt;""),1,0)</x:f>
+      <x:c r="F74" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G74" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H74" s="12" t="str"/>
@@ -4218,6 +4191,10 @@
         <x:v>T07; M-027,M-028; L-08; Consolidação 13/09/2026, pendência 4; Fechamento vigente 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M74" s="10" t="n">
+        <x:f>IF(AND(E74="Concluída",H74&lt;&gt;""),F74,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N74" s="10" t="n">
         <x:f>F74*G74</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4238,11 +4215,10 @@
       <x:c r="E75" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F75" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G75" s="32" t="n">
-        <x:f>IF(AND(E75="Concluída",H75&lt;&gt;""),1,0)</x:f>
+      <x:c r="F75" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G75" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="12" t="str"/>
@@ -4259,6 +4235,10 @@
         <x:v>T07; Fechamento vigente 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M75" s="11" t="n">
+        <x:f>IF(AND(E75="Concluída",H75&lt;&gt;""),F75,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N75" s="11" t="n">
         <x:f>F75*G75</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4279,11 +4259,10 @@
       <x:c r="E76" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F76" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G76" s="31" t="n">
-        <x:f>IF(AND(E76="Concluída",H76&lt;&gt;""),1,0)</x:f>
+      <x:c r="F76" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G76" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="12" t="str"/>
@@ -4300,6 +4279,10 @@
         <x:v>T08 indicadores PMR/PMP/PME e ciclo; B_Intersecoes!A12:I12</x:v>
       </x:c>
       <x:c r="M76" s="10" t="n">
+        <x:f>IF(AND(E76="Concluída",H76&lt;&gt;""),F76,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N76" s="10" t="n">
         <x:f>F76*G76</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4320,11 +4303,10 @@
       <x:c r="E77" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F77" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G77" s="32" t="n">
-        <x:f>IF(AND(E77="Concluída",H77&lt;&gt;""),1,0)</x:f>
+      <x:c r="F77" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="12" t="str"/>
@@ -4341,6 +4323,10 @@
         <x:v>M-030..M-034; T08; Consolidação 13/09/2026, §§4–7; Fechamento vigente 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M77" s="11" t="n">
+        <x:f>IF(AND(E77="Concluída",H77&lt;&gt;""),F77,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N77" s="11" t="n">
         <x:f>F77*G77</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4361,11 +4347,10 @@
       <x:c r="E78" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F78" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G78" s="31" t="n">
-        <x:f>IF(AND(E78="Concluída",H78&lt;&gt;""),1,0)</x:f>
+      <x:c r="F78" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G78" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="12" t="str"/>
@@ -4382,6 +4367,10 @@
         <x:v>T08; M-034; C-02,C-03,L-07; Consolidação 13/09/2026, §§6–9; Fechamento vigente 13/09/2026, §§1–2</x:v>
       </x:c>
       <x:c r="M78" s="10" t="n">
+        <x:f>IF(AND(E78="Concluída",H78&lt;&gt;""),F78,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N78" s="10" t="n">
         <x:f>F78*G78</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4402,11 +4391,10 @@
       <x:c r="E79" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F79" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G79" s="32" t="n">
-        <x:f>IF(AND(E79="Concluída",H79&lt;&gt;""),1,0)</x:f>
+      <x:c r="F79" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="12" t="str"/>
@@ -4423,6 +4411,10 @@
         <x:v>T08; T16 regra Tela 08 não exporta; Consolidação 13/09/2026, §§6–9</x:v>
       </x:c>
       <x:c r="M79" s="11" t="n">
+        <x:f>IF(AND(E79="Concluída",H79&lt;&gt;""),F79,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N79" s="11" t="n">
         <x:f>F79*G79</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4443,11 +4435,10 @@
       <x:c r="E80" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F80" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G80" s="31" t="n">
-        <x:f>IF(AND(E80="Concluída",H80&lt;&gt;""),1,0)</x:f>
+      <x:c r="F80" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H80" s="12" t="str"/>
@@ -4464,6 +4455,10 @@
         <x:v>Menus; T08 Ver aplicações; Consolidação 13/09/2026, §§4–7</x:v>
       </x:c>
       <x:c r="M80" s="10" t="n">
+        <x:f>IF(AND(E80="Concluída",H80&lt;&gt;""),F80,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N80" s="10" t="n">
         <x:f>F80*G80</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4484,11 +4479,10 @@
       <x:c r="E81" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F81" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G81" s="32" t="n">
-        <x:f>IF(AND(E81="Concluída",H81&lt;&gt;""),1,0)</x:f>
+      <x:c r="F81" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="12" t="str"/>
@@ -4505,6 +4499,10 @@
         <x:v>M-021..M-023; L-06,L-10; Fechamento vigente 13/09/2026, §3.3</x:v>
       </x:c>
       <x:c r="M81" s="11" t="n">
+        <x:f>IF(AND(E81="Concluída",H81&lt;&gt;""),F81,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N81" s="11" t="n">
         <x:f>F81*G81</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4525,11 +4523,10 @@
       <x:c r="E82" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F82" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G82" s="31" t="n">
-        <x:f>IF(AND(E82="Concluída",H82&lt;&gt;""),1,0)</x:f>
+      <x:c r="F82" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G82" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H82" s="12" t="str"/>
@@ -4546,6 +4543,10 @@
         <x:v>M-013..M-016; L-16; Consolidação 13/09/2026, §12</x:v>
       </x:c>
       <x:c r="M82" s="10" t="n">
+        <x:f>IF(AND(E82="Concluída",H82&lt;&gt;""),F82,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N82" s="10" t="n">
         <x:f>F82*G82</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4566,11 +4567,10 @@
       <x:c r="E83" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F83" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G83" s="32" t="n">
-        <x:f>IF(AND(E83="Concluída",H83&lt;&gt;""),1,0)</x:f>
+      <x:c r="F83" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="12" t="str"/>
@@ -4587,6 +4587,10 @@
         <x:v>T09; Q_CEI_Tela_11; Consolidação 13/09/2026, §3; Fechamento vigente 13/09/2026, §3</x:v>
       </x:c>
       <x:c r="M83" s="11" t="n">
+        <x:f>IF(AND(E83="Concluída",H83&lt;&gt;""),F83,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N83" s="11" t="n">
         <x:f>F83*G83</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4607,11 +4611,10 @@
       <x:c r="E84" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F84" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G84" s="31" t="n">
-        <x:f>IF(AND(E84="Concluída",H84&lt;&gt;""),1,0)</x:f>
+      <x:c r="F84" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="12" t="str"/>
@@ -4626,6 +4629,10 @@
         <x:v>T09</x:v>
       </x:c>
       <x:c r="M84" s="10" t="n">
+        <x:f>IF(AND(E84="Concluída",H84&lt;&gt;""),F84,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N84" s="10" t="n">
         <x:f>F84*G84</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4646,11 +4653,10 @@
       <x:c r="E85" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F85" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G85" s="32" t="n">
-        <x:f>IF(AND(E85="Concluída",H85&lt;&gt;""),1,0)</x:f>
+      <x:c r="F85" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="12" t="str"/>
@@ -4667,6 +4673,10 @@
         <x:v>T10; T16 Meta por SKU; Fechamento vigente 13/09/2026, §§4,6.4</x:v>
       </x:c>
       <x:c r="M85" s="11" t="n">
+        <x:f>IF(AND(E85="Concluída",H85&lt;&gt;""),F85,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N85" s="11" t="n">
         <x:f>F85*G85</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4687,11 +4697,10 @@
       <x:c r="E86" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F86" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G86" s="31" t="n">
-        <x:f>IF(AND(E86="Concluída",H86&lt;&gt;""),1,0)</x:f>
+      <x:c r="F86" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="12" t="str"/>
@@ -4708,6 +4717,10 @@
         <x:v>T10; T10 duplicata; Fechamento vigente 13/09/2026, §4.1–4.4</x:v>
       </x:c>
       <x:c r="M86" s="10" t="n">
+        <x:f>IF(AND(E86="Concluída",H86&lt;&gt;""),F86,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N86" s="10" t="n">
         <x:f>F86*G86</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4728,11 +4741,10 @@
       <x:c r="E87" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F87" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G87" s="32" t="n">
-        <x:f>IF(AND(E87="Concluída",H87&lt;&gt;""),1,0)</x:f>
+      <x:c r="F87" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="12" t="str"/>
@@ -4749,6 +4761,10 @@
         <x:v>T10; M-052; Fechamento vigente 13/09/2026, §4.2–4.4</x:v>
       </x:c>
       <x:c r="M87" s="11" t="n">
+        <x:f>IF(AND(E87="Concluída",H87&lt;&gt;""),F87,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N87" s="11" t="n">
         <x:f>F87*G87</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4769,11 +4785,10 @@
       <x:c r="E88" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F88" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G88" s="31" t="n">
-        <x:f>IF(AND(E88="Concluída",H88&lt;&gt;""),1,0)</x:f>
+      <x:c r="F88" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="12" t="str"/>
@@ -4790,6 +4805,10 @@
         <x:v>M-042; Q_CEI_Tela_11; Fechamento vigente 13/09/2026, §3.1–3.2</x:v>
       </x:c>
       <x:c r="M88" s="10" t="n">
+        <x:f>IF(AND(E88="Concluída",H88&lt;&gt;""),F88,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N88" s="10" t="n">
         <x:f>F88*G88</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4810,11 +4829,10 @@
       <x:c r="E89" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F89" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G89" s="32" t="n">
-        <x:f>IF(AND(E89="Concluída",H89&lt;&gt;""),1,0)</x:f>
+      <x:c r="F89" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H89" s="12" t="str"/>
@@ -4831,6 +4849,10 @@
         <x:v>M-043; H_Contrato_Dados!A19:H20</x:v>
       </x:c>
       <x:c r="M89" s="11" t="n">
+        <x:f>IF(AND(E89="Concluída",H89&lt;&gt;""),F89,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N89" s="11" t="n">
         <x:f>F89*G89</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4851,11 +4873,10 @@
       <x:c r="E90" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F90" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G90" s="31" t="n">
-        <x:f>IF(AND(E90="Concluída",H90&lt;&gt;""),1,0)</x:f>
+      <x:c r="F90" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H90" s="12" t="str"/>
@@ -4872,6 +4893,10 @@
         <x:v>L-15,L-17,L-18; Q_CEI_Tela_11; Fechamento vigente 13/09/2026, §3.1–3.3</x:v>
       </x:c>
       <x:c r="M90" s="10" t="n">
+        <x:f>IF(AND(E90="Concluída",H90&lt;&gt;""),F90,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N90" s="10" t="n">
         <x:f>F90*G90</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4892,11 +4917,10 @@
       <x:c r="E91" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F91" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G91" s="32" t="n">
-        <x:f>IF(AND(E91="Concluída",H91&lt;&gt;""),1,0)</x:f>
+      <x:c r="F91" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H91" s="12" t="str"/>
@@ -4913,6 +4937,10 @@
         <x:v>M-044; Q_CEI_Tela_11; Consolidação 13/09/2026, pendência 10; Fechamento vigente 13/09/2026, §3.4</x:v>
       </x:c>
       <x:c r="M91" s="11" t="n">
+        <x:f>IF(AND(E91="Concluída",H91&lt;&gt;""),F91,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N91" s="11" t="n">
         <x:f>F91*G91</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4925,7 +4953,7 @@
         <x:v>07 Estoque, produção e compras</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>Implementar T11 Compras e exportação de recomendações</x:v>
+        <x:v>Implementar T11 Compras para consulta</x:v>
       </x:c>
       <x:c r="D92" s="10" t="str">
         <x:v>Desenvolvimento</x:v>
@@ -4933,11 +4961,10 @@
       <x:c r="E92" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F92" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G92" s="31" t="n">
-        <x:f>IF(AND(E92="Concluída",H92&lt;&gt;""),1,0)</x:f>
+      <x:c r="F92" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G92" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H92" s="12" t="str"/>
@@ -4954,6 +4981,10 @@
         <x:v>Q_CEI_Tela_11; T-CEI11-01..12; Fechamento vigente 13/09/2026, §§3.4,5</x:v>
       </x:c>
       <x:c r="M92" s="10" t="n">
+        <x:f>IF(AND(E92="Concluída",H92&lt;&gt;""),F92,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N92" s="10" t="n">
         <x:f>F92*G92</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4974,11 +5005,10 @@
       <x:c r="E93" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F93" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G93" s="32" t="n">
-        <x:f>IF(AND(E93="Concluída",H93&lt;&gt;""),1,0)</x:f>
+      <x:c r="F93" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G93" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H93" s="12" t="str"/>
@@ -4995,6 +5025,10 @@
         <x:v>R_CEI_Tela_12; Consolidação 13/09/2026, pendência 9</x:v>
       </x:c>
       <x:c r="M93" s="11" t="n">
+        <x:f>IF(AND(E93="Concluída",H93&lt;&gt;""),F93,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N93" s="11" t="n">
         <x:f>F93*G93</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5015,11 +5049,10 @@
       <x:c r="E94" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F94" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G94" s="31" t="n">
-        <x:f>IF(AND(E94="Concluída",H94&lt;&gt;""),1,0)</x:f>
+      <x:c r="F94" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H94" s="12" t="str"/>
@@ -5034,6 +5067,10 @@
         <x:v>H_Contrato_Dados!A23:H23; T12</x:v>
       </x:c>
       <x:c r="M94" s="10" t="n">
+        <x:f>IF(AND(E94="Concluída",H94&lt;&gt;""),F94,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N94" s="10" t="n">
         <x:f>F94*G94</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5054,11 +5091,10 @@
       <x:c r="E95" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F95" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G95" s="32" t="n">
-        <x:f>IF(AND(E95="Concluída",H95&lt;&gt;""),1,0)</x:f>
+      <x:c r="F95" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G95" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="12" t="str"/>
@@ -5075,6 +5111,10 @@
         <x:v>M-046; R_CEI_Tela_12</x:v>
       </x:c>
       <x:c r="M95" s="11" t="n">
+        <x:f>IF(AND(E95="Concluída",H95&lt;&gt;""),F95,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N95" s="11" t="n">
         <x:f>F95*G95</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5095,11 +5135,10 @@
       <x:c r="E96" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F96" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G96" s="31" t="n">
-        <x:f>IF(AND(E96="Concluída",H96&lt;&gt;""),1,0)</x:f>
+      <x:c r="F96" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G96" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H96" s="12" t="str"/>
@@ -5116,6 +5155,10 @@
         <x:v>L-20; T-CEI12-01,02,10; Consolidação 13/09/2026, pendência 9</x:v>
       </x:c>
       <x:c r="M96" s="10" t="n">
+        <x:f>IF(AND(E96="Concluída",H96&lt;&gt;""),F96,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N96" s="10" t="n">
         <x:f>F96*G96</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5136,11 +5179,10 @@
       <x:c r="E97" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F97" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G97" s="32" t="n">
-        <x:f>IF(AND(E97="Concluída",H97&lt;&gt;""),1,0)</x:f>
+      <x:c r="F97" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G97" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H97" s="12" t="str"/>
@@ -5157,6 +5199,10 @@
         <x:v>M-048; L-21; R_CEI_Tela_12; Fechamento vigente 13/09/2026, §4.6</x:v>
       </x:c>
       <x:c r="M97" s="11" t="n">
+        <x:f>IF(AND(E97="Concluída",H97&lt;&gt;""),F97,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N97" s="11" t="n">
         <x:f>F97*G97</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5177,11 +5223,10 @@
       <x:c r="E98" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F98" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G98" s="31" t="n">
-        <x:f>IF(AND(E98="Concluída",H98&lt;&gt;""),1,0)</x:f>
+      <x:c r="F98" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="12" t="str"/>
@@ -5198,6 +5243,10 @@
         <x:v>M-047; R_CEI_Tela_12; Fechamento vigente 13/09/2026, §4.5</x:v>
       </x:c>
       <x:c r="M98" s="10" t="n">
+        <x:f>IF(AND(E98="Concluída",H98&lt;&gt;""),F98,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N98" s="10" t="n">
         <x:f>F98*G98</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5218,11 +5267,10 @@
       <x:c r="E99" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F99" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G99" s="32" t="n">
-        <x:f>IF(AND(E99="Concluída",H99&lt;&gt;""),1,0)</x:f>
+      <x:c r="F99" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="12" t="str"/>
@@ -5239,6 +5287,10 @@
         <x:v>M-047; H_Contrato_Dados!A28:H28; Fechamento vigente 13/09/2026, §4.5</x:v>
       </x:c>
       <x:c r="M99" s="11" t="n">
+        <x:f>IF(AND(E99="Concluída",H99&lt;&gt;""),F99,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N99" s="11" t="n">
         <x:f>F99*G99</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5259,11 +5311,10 @@
       <x:c r="E100" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F100" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G100" s="31" t="n">
-        <x:f>IF(AND(E100="Concluída",H100&lt;&gt;""),1,0)</x:f>
+      <x:c r="F100" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G100" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="12" t="str"/>
@@ -5280,6 +5331,10 @@
         <x:v>H_Contrato_Dados!A12:H12; R_CEI_Tela_12; Consolidação 13/09/2026, §11; pendência 7; Fechamento vigente 13/09/2026, §3.1,4.5</x:v>
       </x:c>
       <x:c r="M100" s="10" t="n">
+        <x:f>IF(AND(E100="Concluída",H100&lt;&gt;""),F100,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N100" s="10" t="n">
         <x:f>F100*G100</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5300,11 +5355,10 @@
       <x:c r="E101" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F101" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G101" s="32" t="n">
-        <x:f>IF(AND(E101="Concluída",H101&lt;&gt;""),1,0)</x:f>
+      <x:c r="F101" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G101" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="12" t="str"/>
@@ -5321,6 +5375,10 @@
         <x:v>T12 aba Resumo financeiro; R_CEI_Tela_12; Fechamento vigente 13/09/2026, §4.6</x:v>
       </x:c>
       <x:c r="M101" s="11" t="n">
+        <x:f>IF(AND(E101="Concluída",H101&lt;&gt;""),F101,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N101" s="11" t="n">
         <x:f>F101*G101</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5341,11 +5399,10 @@
       <x:c r="E102" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F102" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G102" s="31" t="n">
-        <x:f>IF(AND(E102="Concluída",H102&lt;&gt;""),1,0)</x:f>
+      <x:c r="F102" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G102" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="12" t="str"/>
@@ -5362,6 +5419,10 @@
         <x:v>T12; R_CEI_Tela_12; Fechamento vigente 13/09/2026, §§4–5</x:v>
       </x:c>
       <x:c r="M102" s="10" t="n">
+        <x:f>IF(AND(E102="Concluída",H102&lt;&gt;""),F102,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N102" s="10" t="n">
         <x:f>F102*G102</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5382,11 +5443,10 @@
       <x:c r="E103" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F103" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G103" s="32" t="n">
-        <x:f>IF(AND(E103="Concluída",H103&lt;&gt;""),1,0)</x:f>
+      <x:c r="F103" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G103" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="12" t="str"/>
@@ -5403,6 +5463,10 @@
         <x:v>M-049; R_CEI_Tela_12; T-CEI12-11..13</x:v>
       </x:c>
       <x:c r="M103" s="11" t="n">
+        <x:f>IF(AND(E103="Concluída",H103&lt;&gt;""),F103,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N103" s="11" t="n">
         <x:f>F103*G103</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5423,11 +5487,10 @@
       <x:c r="E104" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F104" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G104" s="31" t="n">
-        <x:f>IF(AND(E104="Concluída",H104&lt;&gt;""),1,0)</x:f>
+      <x:c r="F104" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G104" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H104" s="12" t="str"/>
@@ -5444,6 +5507,10 @@
         <x:v>M-051,M-054; S_CEI_Tela_13; Consolidação 13/09/2026, §§2–7</x:v>
       </x:c>
       <x:c r="M104" s="10" t="n">
+        <x:f>IF(AND(E104="Concluída",H104&lt;&gt;""),F104,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N104" s="10" t="n">
         <x:f>F104*G104</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5464,11 +5531,10 @@
       <x:c r="E105" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F105" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G105" s="32" t="n">
-        <x:f>IF(AND(E105="Concluída",H105&lt;&gt;""),1,0)</x:f>
+      <x:c r="F105" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G105" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H105" s="12" t="str"/>
@@ -5483,6 +5549,10 @@
         <x:v>T13; S_CEI_Tela_13</x:v>
       </x:c>
       <x:c r="M105" s="11" t="n">
+        <x:f>IF(AND(E105="Concluída",H105&lt;&gt;""),F105,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N105" s="11" t="n">
         <x:f>F105*G105</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5503,11 +5573,10 @@
       <x:c r="E106" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F106" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G106" s="31" t="n">
-        <x:f>IF(AND(E106="Concluída",H106&lt;&gt;""),1,0)</x:f>
+      <x:c r="F106" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H106" s="12" t="str"/>
@@ -5522,6 +5591,10 @@
         <x:v>M-052,M-054; T_CEI_Tela_14</x:v>
       </x:c>
       <x:c r="M106" s="10" t="n">
+        <x:f>IF(AND(E106="Concluída",H106&lt;&gt;""),F106,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N106" s="10" t="n">
         <x:f>F106*G106</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5542,11 +5615,10 @@
       <x:c r="E107" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F107" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G107" s="32" t="n">
-        <x:f>IF(AND(E107="Concluída",H107&lt;&gt;""),1,0)</x:f>
+      <x:c r="F107" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H107" s="12" t="str"/>
@@ -5561,6 +5633,10 @@
         <x:v>T14; T_CEI_Tela_14</x:v>
       </x:c>
       <x:c r="M107" s="11" t="n">
+        <x:f>IF(AND(E107="Concluída",H107&lt;&gt;""),F107,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N107" s="11" t="n">
         <x:f>F107*G107</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5581,11 +5657,10 @@
       <x:c r="E108" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F108" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G108" s="31" t="n">
-        <x:f>IF(AND(E108="Concluída",H108&lt;&gt;""),1,0)</x:f>
+      <x:c r="F108" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H108" s="12" t="str"/>
@@ -5602,6 +5677,10 @@
         <x:v>Menus: Visão Executiva; Fechamento vigente 13/09/2026, §4.2,5</x:v>
       </x:c>
       <x:c r="M108" s="10" t="n">
+        <x:f>IF(AND(E108="Concluída",H108&lt;&gt;""),F108,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N108" s="10" t="n">
         <x:f>F108*G108</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5622,11 +5701,10 @@
       <x:c r="E109" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F109" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G109" s="32" t="n">
-        <x:f>IF(AND(E109="Concluída",H109&lt;&gt;""),1,0)</x:f>
+      <x:c r="F109" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="12" t="str"/>
@@ -5643,6 +5721,10 @@
         <x:v>Menus T12/T13; matriz Pricing/Logística; Fechamento vigente 13/09/2026, §5</x:v>
       </x:c>
       <x:c r="M109" s="11" t="n">
+        <x:f>IF(AND(E109="Concluída",H109&lt;&gt;""),F109,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N109" s="11" t="n">
         <x:f>F109*G109</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5663,11 +5745,10 @@
       <x:c r="E110" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F110" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G110" s="31" t="n">
-        <x:f>IF(AND(E110="Concluída",H110&lt;&gt;""),1,0)</x:f>
+      <x:c r="F110" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H110" s="12" t="str"/>
@@ -5684,6 +5765,10 @@
         <x:v>T02–T07; T13–T15; L-22; Fechamento vigente 13/09/2026, §5.7</x:v>
       </x:c>
       <x:c r="M110" s="10" t="n">
+        <x:f>IF(AND(E110="Concluída",H110&lt;&gt;""),F110,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N110" s="10" t="n">
         <x:f>F110*G110</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5704,11 +5789,10 @@
       <x:c r="E111" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F111" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G111" s="32" t="n">
-        <x:f>IF(AND(E111="Concluída",H111&lt;&gt;""),1,0)</x:f>
+      <x:c r="F111" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G111" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H111" s="12" t="str"/>
@@ -5723,6 +5807,10 @@
         <x:v>A_Matriz_Mestra; H_Contrato_Dados; I_Testes; Consolidação 13/09/2026, consolidação integral; Fechamento vigente 13/09/2026, integral</x:v>
       </x:c>
       <x:c r="M111" s="11" t="n">
+        <x:f>IF(AND(E111="Concluída",H111&lt;&gt;""),F111,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N111" s="11" t="n">
         <x:f>F111*G111</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5743,11 +5831,10 @@
       <x:c r="E112" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F112" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G112" s="31" t="n">
-        <x:f>IF(AND(E112="Concluída",H112&lt;&gt;""),1,0)</x:f>
+      <x:c r="F112" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H112" s="12" t="str"/>
@@ -5762,6 +5849,10 @@
         <x:v>I_Testes: catálogo previsto, ainda não executado; Consolidação 13/09/2026, §§6–12; Fechamento vigente 13/09/2026, §§2–4,6,8</x:v>
       </x:c>
       <x:c r="M112" s="10" t="n">
+        <x:f>IF(AND(E112="Concluída",H112&lt;&gt;""),F112,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N112" s="10" t="n">
         <x:f>F112*G112</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5782,11 +5873,10 @@
       <x:c r="E113" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F113" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G113" s="32" t="n">
-        <x:f>IF(AND(E113="Concluída",H113&lt;&gt;""),1,0)</x:f>
+      <x:c r="F113" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H113" s="12" t="str"/>
@@ -5803,6 +5893,10 @@
         <x:v>; Consolidação 13/09/2026, §§1–2,6–10; Fechamento vigente 13/09/2026, §§7–8</x:v>
       </x:c>
       <x:c r="M113" s="11" t="n">
+        <x:f>IF(AND(E113="Concluída",H113&lt;&gt;""),F113,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N113" s="11" t="n">
         <x:f>F113*G113</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5823,11 +5917,10 @@
       <x:c r="E114" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F114" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G114" s="31" t="n">
-        <x:f>IF(AND(E114="Concluída",H114&lt;&gt;""),1,0)</x:f>
+      <x:c r="F114" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H114" s="12" t="str"/>
@@ -5844,6 +5937,10 @@
         <x:v>Todas as imagens e decisões UX; Fechamento vigente 13/09/2026, §5</x:v>
       </x:c>
       <x:c r="M114" s="10" t="n">
+        <x:f>IF(AND(E114="Concluída",H114&lt;&gt;""),F114,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N114" s="10" t="n">
         <x:f>F114*G114</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5864,11 +5961,10 @@
       <x:c r="E115" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F115" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G115" s="32" t="n">
-        <x:f>IF(AND(E115="Concluída",H115&lt;&gt;""),1,0)</x:f>
+      <x:c r="F115" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G115" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H115" s="12" t="str"/>
@@ -5885,6 +5981,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M115" s="11" t="n">
+        <x:f>IF(AND(E115="Concluída",H115&lt;&gt;""),F115,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N115" s="11" t="n">
         <x:f>F115*G115</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5905,11 +6005,10 @@
       <x:c r="E116" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F116" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G116" s="31" t="n">
-        <x:f>IF(AND(E116="Concluída",H116&lt;&gt;""),1,0)</x:f>
+      <x:c r="F116" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G116" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H116" s="12" t="str"/>
@@ -5924,6 +6023,10 @@
         <x:v>; Fechamento vigente 13/09/2026, §§1–8; Fechamento vigente 13/09/2026, §8.14</x:v>
       </x:c>
       <x:c r="M116" s="10" t="n">
+        <x:f>IF(AND(E116="Concluída",H116&lt;&gt;""),F116,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N116" s="10" t="n">
         <x:f>F116*G116</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5944,11 +6047,10 @@
       <x:c r="E117" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F117" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G117" s="32" t="n">
-        <x:f>IF(AND(E117="Concluída",H117&lt;&gt;""),1,0)</x:f>
+      <x:c r="F117" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G117" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="12" t="str"/>
@@ -5963,6 +6065,10 @@
         <x:v>; Consolidação 13/09/2026, §2</x:v>
       </x:c>
       <x:c r="M117" s="11" t="n">
+        <x:f>IF(AND(E117="Concluída",H117&lt;&gt;""),F117,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N117" s="11" t="n">
         <x:f>F117*G117</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5983,11 +6089,10 @@
       <x:c r="E118" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F118" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G118" s="31" t="n">
-        <x:f>IF(AND(E118="Concluída",H118&lt;&gt;""),1,0)</x:f>
+      <x:c r="F118" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G118" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="12" t="str"/>
@@ -6002,6 +6107,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M118" s="10" t="n">
+        <x:f>IF(AND(E118="Concluída",H118&lt;&gt;""),F118,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N118" s="10" t="n">
         <x:f>F118*G118</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6022,11 +6131,10 @@
       <x:c r="E119" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F119" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G119" s="32" t="n">
-        <x:f>IF(AND(E119="Concluída",H119&lt;&gt;""),1,0)</x:f>
+      <x:c r="F119" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G119" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H119" s="12" t="str"/>
@@ -6041,6 +6149,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M119" s="11" t="n">
+        <x:f>IF(AND(E119="Concluída",H119&lt;&gt;""),F119,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N119" s="11" t="n">
         <x:f>F119*G119</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6061,11 +6173,10 @@
       <x:c r="E120" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F120" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G120" s="31" t="n">
-        <x:f>IF(AND(E120="Concluída",H120&lt;&gt;""),1,0)</x:f>
+      <x:c r="F120" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G120" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H120" s="12" t="str"/>
@@ -6082,6 +6193,10 @@
         <x:v>; Consolidação 13/09/2026, §§1–2; Fechamento vigente 13/09/2026, §7</x:v>
       </x:c>
       <x:c r="M120" s="10" t="n">
+        <x:f>IF(AND(E120="Concluída",H120&lt;&gt;""),F120,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N120" s="10" t="n">
         <x:f>F120*G120</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6102,11 +6217,10 @@
       <x:c r="E121" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F121" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G121" s="32" t="n">
-        <x:f>IF(AND(E121="Concluída",H121&lt;&gt;""),1,0)</x:f>
+      <x:c r="F121" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G121" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="12" t="str"/>
@@ -6123,6 +6237,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M121" s="11" t="n">
+        <x:f>IF(AND(E121="Concluída",H121&lt;&gt;""),F121,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N121" s="11" t="n">
         <x:f>F121*G121</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6143,11 +6261,10 @@
       <x:c r="E122" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F122" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G122" s="31" t="n">
-        <x:f>IF(AND(E122="Concluída",H122&lt;&gt;""),1,0)</x:f>
+      <x:c r="F122" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G122" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H122" s="12" t="str"/>
@@ -6162,6 +6279,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M122" s="10" t="n">
+        <x:f>IF(AND(E122="Concluída",H122&lt;&gt;""),F122,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N122" s="10" t="n">
         <x:f>F122*G122</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6182,11 +6303,10 @@
       <x:c r="E123" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F123" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G123" s="32" t="n">
-        <x:f>IF(AND(E123="Concluída",H123&lt;&gt;""),1,0)</x:f>
+      <x:c r="F123" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G123" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H123" s="12" t="str"/>
@@ -6201,6 +6321,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M123" s="11" t="n">
+        <x:f>IF(AND(E123="Concluída",H123&lt;&gt;""),F123,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N123" s="11" t="n">
         <x:f>F123*G123</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6221,11 +6345,10 @@
       <x:c r="E124" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F124" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G124" s="31" t="n">
-        <x:f>IF(AND(E124="Concluída",H124&lt;&gt;""),1,0)</x:f>
+      <x:c r="F124" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G124" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H124" s="12" t="str"/>
@@ -6242,6 +6365,10 @@
         <x:v>; Consolidação 13/09/2026, §2; Fechamento vigente 13/09/2026, §7.5</x:v>
       </x:c>
       <x:c r="M124" s="10" t="n">
+        <x:f>IF(AND(E124="Concluída",H124&lt;&gt;""),F124,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N124" s="10" t="n">
         <x:f>F124*G124</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6262,11 +6389,10 @@
       <x:c r="E125" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F125" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G125" s="32" t="n">
-        <x:f>IF(AND(E125="Concluída",H125&lt;&gt;""),1,0)</x:f>
+      <x:c r="F125" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G125" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H125" s="12" t="str"/>
@@ -6283,6 +6409,10 @@
         <x:v>; Consolidação 13/09/2026, §2; Fechamento vigente 13/09/2026, §7.6</x:v>
       </x:c>
       <x:c r="M125" s="11" t="n">
+        <x:f>IF(AND(E125="Concluída",H125&lt;&gt;""),F125,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N125" s="11" t="n">
         <x:f>F125*G125</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6303,11 +6433,10 @@
       <x:c r="E126" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F126" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G126" s="31" t="n">
-        <x:f>IF(AND(E126="Concluída",H126&lt;&gt;""),1,0)</x:f>
+      <x:c r="F126" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G126" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H126" s="12" t="str"/>
@@ -6324,6 +6453,10 @@
         <x:v>; Fechamento vigente 13/09/2026, §7.7–7.8</x:v>
       </x:c>
       <x:c r="M126" s="10" t="n">
+        <x:f>IF(AND(E126="Concluída",H126&lt;&gt;""),F126,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N126" s="10" t="n">
         <x:f>F126*G126</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6344,11 +6477,10 @@
       <x:c r="E127" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F127" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G127" s="32" t="n">
-        <x:f>IF(AND(E127="Concluída",H127&lt;&gt;""),1,0)</x:f>
+      <x:c r="F127" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G127" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H127" s="12" t="str"/>
@@ -6363,6 +6495,10 @@
         <x:v>; Consolidação 13/09/2026, §§1–2; pendência 9</x:v>
       </x:c>
       <x:c r="M127" s="11" t="n">
+        <x:f>IF(AND(E127="Concluída",H127&lt;&gt;""),F127,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N127" s="11" t="n">
         <x:f>F127*G127</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6383,11 +6519,10 @@
       <x:c r="E128" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F128" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G128" s="31" t="n">
-        <x:f>IF(AND(E128="Concluída",H128&lt;&gt;""),1,0)</x:f>
+      <x:c r="F128" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G128" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H128" s="12" t="str"/>
@@ -6402,6 +6537,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M128" s="10" t="n">
+        <x:f>IF(AND(E128="Concluída",H128&lt;&gt;""),F128,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N128" s="10" t="n">
         <x:f>F128*G128</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6422,11 +6561,10 @@
       <x:c r="E129" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F129" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G129" s="32" t="n">
-        <x:f>IF(AND(E129="Concluída",H129&lt;&gt;""),1,0)</x:f>
+      <x:c r="F129" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G129" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H129" s="12" t="str"/>
@@ -6443,6 +6581,10 @@
         <x:v>; Consolidação 13/09/2026, §§1–2,10; Fechamento vigente 13/09/2026, §§7–8</x:v>
       </x:c>
       <x:c r="M129" s="11" t="n">
+        <x:f>IF(AND(E129="Concluída",H129&lt;&gt;""),F129,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N129" s="11" t="n">
         <x:f>F129*G129</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6463,11 +6605,10 @@
       <x:c r="E130" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F130" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G130" s="31" t="n">
-        <x:f>IF(AND(E130="Concluída",H130&lt;&gt;""),1,0)</x:f>
+      <x:c r="F130" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G130" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H130" s="12" t="str"/>
@@ -6482,6 +6623,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M130" s="10" t="n">
+        <x:f>IF(AND(E130="Concluída",H130&lt;&gt;""),F130,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N130" s="10" t="n">
         <x:f>F130*G130</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6502,11 +6647,10 @@
       <x:c r="E131" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F131" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G131" s="32" t="n">
-        <x:f>IF(AND(E131="Concluída",H131&lt;&gt;""),1,0)</x:f>
+      <x:c r="F131" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G131" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="12" t="str"/>
@@ -6521,6 +6665,10 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M131" s="11" t="n">
+        <x:f>IF(AND(E131="Concluída",H131&lt;&gt;""),F131,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N131" s="11" t="n">
         <x:f>F131*G131</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6541,11 +6689,10 @@
       <x:c r="E132" s="12" t="str">
         <x:v>Não iniciada</x:v>
       </x:c>
-      <x:c r="F132" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G132" s="31" t="n">
-        <x:f>IF(AND(E132="Concluída",H132&lt;&gt;""),1,0)</x:f>
+      <x:c r="F132" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G132" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="12" t="str"/>
@@ -6560,144 +6707,126 @@
         <x:v>Necessidade técnica de entrega e operação.</x:v>
       </x:c>
       <x:c r="M132" s="10" t="n">
+        <x:f>IF(AND(E132="Concluída",H132&lt;&gt;""),F132,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N132" s="10" t="n">
         <x:f>F132*G132</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:H132">
+  <x:conditionalFormatting sqref="A6:N132">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>AND($E6="Concluída",$H6="")</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="E6:E132">
+    <x:dataValidation type="list" sqref="E6:E132">
       <x:formula1>"Não iniciada,Aguarda decisão,Em andamento,Em validação,Bloqueada,Concluída"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F6:F132">
+    <x:dataValidation type="whole" operator="between" sqref="F6:F132">
       <x:formula1>1</x:formula1>
       <x:formula2>100</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03b99404c46340d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d154634219a4a34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.380000114440918" customWidth="1"/>
-    <x:col min="2" max="2" width="23.1299991607666" customWidth="1"/>
-    <x:col min="3" max="3" width="23.1299991607666" customWidth="1"/>
-    <x:col min="4" max="4" width="70" customWidth="1"/>
-    <x:col min="5" max="5" width="42.5" customWidth="1"/>
-    <x:col min="6" max="6" width="60" customWidth="1"/>
-    <x:col min="7" max="7" width="34.380001068115234" customWidth="1"/>
-    <x:col min="8" max="8" width="28.75" customWidth="1"/>
-    <x:col min="9" max="9" width="31.8799991607666" customWidth="1"/>
+    <x:col min="1" max="1" width="9.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42.5" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34.380001068115234" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="31.8799991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="2" t="n"/>
-      <x:c r="B1" s="2" t="n"/>
-      <x:c r="C1" s="2" t="n"/>
-      <x:c r="D1" s="2" t="n"/>
-      <x:c r="E1" s="2" t="n"/>
-      <x:c r="F1" s="2" t="n"/>
-      <x:c r="G1" s="2" t="n"/>
-      <x:c r="H1" s="2" t="n"/>
-      <x:c r="I1" s="2" t="n"/>
+      <x:c r="A1" s="2"/>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Majucau — regras e verificações</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="n"/>
-      <x:c r="C2" s="2" t="n"/>
-      <x:c r="D2" s="2" t="n"/>
-      <x:c r="E2" s="2" t="n"/>
-      <x:c r="F2" s="2" t="n"/>
-      <x:c r="G2" s="2" t="n"/>
-      <x:c r="H2" s="2" t="n"/>
-      <x:c r="I2" s="2" t="n"/>
+      <x:c r="A2" s="3" t="str">
+        <x:v>Majucau — regras e verificações</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+      <x:c r="I2" s="2"/>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Regras funcionais fechadas. Execução técnica e localização de referências são acompanhadas sem reabrir o negócio.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="2" t="n"/>
-      <x:c r="C3" s="2" t="n"/>
-      <x:c r="D3" s="2" t="n"/>
-      <x:c r="E3" s="2" t="n"/>
-      <x:c r="F3" s="2" t="n"/>
-      <x:c r="G3" s="2" t="n"/>
-      <x:c r="H3" s="2" t="n"/>
-      <x:c r="I3" s="2" t="n"/>
+      <x:c r="A3" s="2" t="str">
+        <x:v>Regras funcionais fechadas. Execução técnica e localização de referências são acompanhadas sem reabrir o negócio.</x:v>
+      </x:c>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+      <x:c r="I3" s="2"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="2" t="n"/>
-      <x:c r="B4" s="2" t="n"/>
-      <x:c r="C4" s="2" t="n"/>
-      <x:c r="D4" s="2" t="n"/>
-      <x:c r="E4" s="2" t="n"/>
-      <x:c r="F4" s="2" t="n"/>
-      <x:c r="G4" s="2" t="n"/>
-      <x:c r="H4" s="2" t="n"/>
-      <x:c r="I4" s="2" t="n"/>
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+      <x:c r="I4" s="2"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tema</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Situação</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Definição / verificação necessária</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Impacto</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Resposta registrada</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fonte</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tarefas</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Natureza</x:t>
-        </x:is>
+      <x:c r="A5" s="8" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>Tema</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>Situação</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>Definição / verificação necessária</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>Impacto</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>Resposta registrada</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>Fonte</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
+        <x:v>Tarefas</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>Natureza</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="95" customHeight="1">
@@ -7619,7 +7748,7 @@
         <x:v>Aplicar a definição vigente; execução, evidência e aceite são registrados nas tarefas relacionadas.</x:v>
       </x:c>
       <x:c r="F38" s="12" t="str">
-        <x:v>Exportações previstas/aprovadas permanecem; implementar contrato técnico com mesmos dados/filtros e Excel quando especificado, sem perguntar novamente se a função entra.</x:v>
+        <x:v>Exportações previamente aprovadas continuam previstas, com o mesmo dado e filtro da tela. Exceção aprovada: T11 Compras é somente consulta, sem exportar ou baixar arquivos. Os formatos e contratos por tela permanecem para detalhamento técnico conforme G0-DECISION-REGISTER.md.</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
         <x:v>D_Lacunas!A24:G24; Fechamento das questões ainda tratadas como abertas — 13/09/2026</x:v>
@@ -8112,7 +8241,7 @@
         <x:v>Aplicar a definição vigente; execução, evidência e aceite são registrados nas tarefas relacionadas.</x:v>
       </x:c>
       <x:c r="F55" s="12" t="str">
-        <x:v>Botões e navegação seguem referência aprovada; contrato de execução e exportação é detalhamento técnico, sem redesenhar ou retirar função existente.</x:v>
+        <x:v>Ações seguem as referências aprovadas. T11 Compras permanece somente consulta, sem exportar/baixar ou gerar/alterar pedidos; demais exportações aprovadas são preservadas e detalhadas por tela, sem redesenho.</x:v>
       </x:c>
       <x:c r="G55" s="11" t="str">
         <x:v>T02–T07; T13–T15; L-22; Fechamento das questões ainda tratadas como abertas — 13/09/2026</x:v>
@@ -8141,7 +8270,7 @@
         <x:v>Aplicar a definição vigente; execução, evidência e aceite são registrados nas tarefas relacionadas.</x:v>
       </x:c>
       <x:c r="F56" s="12" t="str">
-        <x:v>Usuário, perfil e capacidade com menor privilégio; atribuição concreta é configuração administrativa explícita na implantação, sem hardcode por pessoa.</x:v>
+        <x:v>Login próprio do Majucau: perfil ADMIN para Financeiro e conta compartilhada para Diretores. Diretores consultam, sincronizam, importam CSV como sincronização e exportam backups e relatórios. A conta compartilhada não identifica qual diretor executou a ação; MFA, sessão, recuperação, provisionamento e autorização efetiva continuam pendentes. Ver G0-DECISION-REGISTER.md.</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
         <x:v>T17; L-26; Fechamento das questões ainda tratadas como abertas — 13/09/2026</x:v>
@@ -9243,7 +9372,7 @@
         <x:v>Aplicar nas tarefas vinculadas e verificar com evidência na implementação futura.</x:v>
       </x:c>
       <x:c r="F94" s="12" t="str">
-        <x:v>O lucro elegível usa a DRE calculada pelo Majucau conforme regras aprovadas, de janeiro até M−2, menos Já Investido (aportes de principal − resgates de principal; rendimentos separados). Seguindo a planilha enviada, o caixa projetado na semana de maior despesa soma o saldo da semana crítica e os recebimentos previstos da Nuvemshop; na integração, confirmar que os recebimentos não estejam já incluídos no saldo para evitar duplicidade. Máximo aplicável = MAX(0; MIN(caixa projetado − reserva mínima de R$ 50.000; lucro elegível)). Valor executável limitado ao saldo transferível do Itaú; tela apenas para consulta. Se a reserva mínima puder ser comprometida, sugerir uma reserva alternativa; o cálculo será definido no documento atualizado pela usuária e não deve ser inventado. Cartão/MDR/parcelas não pertencem à calculadora.</x:v>
+        <x:v>A regra vigente D-003-A usa lucro líquido da DRE própria de janeiro até M−2 menos Já Investido (aportes de principal − resgates de principal; rendimentos separados). O limite de caixa usa o menor saldo diário de fechamento do fluxo consolidado em D0–D+60, sem somar recebimentos da Nuvemshop separadamente. Limite financeiro = MAX(0; menor saldo diário − reserva mínima de R$ 50.000); Máximo Aplicável = MAX(0; MIN(lucro disponível; limite financeiro)). Valor executável limitado ao saldo transferível do Itaú; consulta somente. A sugestão D-003-C é apenas informativa: R$ 50.000 + MAX(0; caixa projetado D0 − menor saldo diário D0–D+60). Estrutura da calculadora preservada; fórmulas antigas da planilha não substituem D-003-A. Fontes reais e integração seguem pendentes; dado ausente permanece indisponível.</x:v>
       </x:c>
       <x:c r="G94" s="10" t="str">
         <x:v>Fechamento das questões ainda tratadas como abertas — 13/09/2026; §1; planilha Calculadora_Aplicacao_Lucro_Liquido_Profissional (1).xlsm enviada em 10/10/2026; esclarecimento posterior da usuária sobre reserva alternativa</x:v>
@@ -9620,7 +9749,7 @@
         <x:v>Aplicar nas tarefas vinculadas e verificar com evidência na implementação futura.</x:v>
       </x:c>
       <x:c r="F107" s="12" t="str">
-        <x:v>Manter exportações aprovadas, inclusive Excel onde especificado. Arquivo usa os mesmos dados, filtros, período, snapshot e métricas da tela.</x:v>
+        <x:v>Manter as exportações aprovadas, incluindo Excel quando especificado, com os mesmos dados, filtros, período, snapshot e métricas da tela. T11 Compras é exceção: somente consulta, sem exportação ou download, conforme aprovação posterior.</x:v>
       </x:c>
       <x:c r="G107" s="11" t="str">
         <x:v>Fechamento das questões ainda tratadas como abertas — 13/09/2026; §5.7</x:v>
@@ -9808,662 +9937,438 @@
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="C6:C113">
+    <x:dataValidation type="list" sqref="C6:C113">
       <x:formula1>"Definida,Execução técnica pendente,Referência a localizar"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R954bf805c8a14ed8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1752f7c26284cf9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22.5" customWidth="1"/>
-    <x:col min="2" max="2" width="36.880001068115234" customWidth="1"/>
-    <x:col min="3" max="3" width="38.130001068115234" customWidth="1"/>
-    <x:col min="4" max="4" width="70" customWidth="1"/>
-    <x:col min="5" max="5" width="15.630000114440918" customWidth="1"/>
+    <x:col min="1" max="1" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="36.880001068115234" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38.130001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.630000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="2" t="n"/>
-      <x:c r="B1" s="2" t="n"/>
-      <x:c r="C1" s="2" t="n"/>
-      <x:c r="D1" s="2" t="n"/>
-      <x:c r="E1" s="2" t="n"/>
+      <x:c r="A1" s="2"/>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Majucau — cobertura dos módulos</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="n"/>
-      <x:c r="C2" s="2" t="n"/>
-      <x:c r="D2" s="2" t="n"/>
-      <x:c r="E2" s="2" t="n"/>
+      <x:c r="A2" s="3" t="str">
+        <x:v>Majucau — cobertura dos módulos</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Balanço Patrimonial foi excluído por decisão atual. Itens incompletos permanecem para refinamento.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="2" t="n"/>
-      <x:c r="C3" s="2" t="n"/>
-      <x:c r="D3" s="2" t="n"/>
-      <x:c r="E3" s="2" t="n"/>
+      <x:c r="A3" s="2" t="str">
+        <x:v>Balanço Patrimonial foi excluído por decisão atual. Itens incompletos permanecem para refinamento.</x:v>
+      </x:c>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="2" t="n"/>
-      <x:c r="B4" s="2" t="n"/>
-      <x:c r="C4" s="2" t="n"/>
-      <x:c r="D4" s="2" t="n"/>
-      <x:c r="E4" s="2" t="n"/>
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Identificação</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Módulo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Material disponível</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Referência</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tarefa de interface</x:t>
-        </x:is>
+      <x:c r="A5" s="8" t="str">
+        <x:v>Identificação</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>Módulo</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>Material disponível</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>Referência</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>Tarefa de interface</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Visão Executiva</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Referência aprovada a localizar no pacote</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Menus; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-102</x:t>
-        </x:is>
+      <x:c r="A6" s="10" t="str">
+        <x:v>T01</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Visão Executiva</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
+        <x:v>Referência aprovada a localizar no pacote</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="str">
+        <x:v>Menus; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="str">
+        <x:v>BK-102</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
-      <x:c r="A7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fluxo de Caixa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T02_Fluxo_de_Caixa.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-062</x:t>
-        </x:is>
+      <x:c r="A7" s="11" t="str">
+        <x:v>T02</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>Fluxo de Caixa</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>T02_Fluxo_de_Caixa.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>BK-062</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contas a Receber</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T03_Contas_a_Receber.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-057</x:t>
-        </x:is>
+      <x:c r="A8" s="10" t="str">
+        <x:v>T03</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>Contas a Receber</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>T03_Contas_a_Receber.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E8" s="10" t="str">
+        <x:v>BK-057</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
-      <x:c r="A9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T04</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contas a Pagar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T04_Contas_a_Pagar.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-059</x:t>
-        </x:is>
+      <x:c r="A9" s="11" t="str">
+        <x:v>T04</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>Contas a Pagar</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>T04_Contas_a_Pagar.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>BK-059</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Conciliação</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T05_Conciliacao.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-055</x:t>
-        </x:is>
+      <x:c r="A10" s="10" t="str">
+        <x:v>T05</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>Conciliação</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>T05_Conciliacao.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E10" s="10" t="str">
+        <x:v>BK-055</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T06</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DRE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T06_DRE.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-067</x:t>
-        </x:is>
+      <x:c r="A11" s="11" t="str">
+        <x:v>T06</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>DRE</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>T06_DRE.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>BK-067</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
-      <x:c r="A12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T07</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Balancete</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T07_Balancete.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-069</x:t>
-        </x:is>
+      <x:c r="A12" s="10" t="str">
+        <x:v>T07</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>Balancete</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>T07_Balancete.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E12" s="10" t="str">
+        <x:v>BK-069</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
-      <x:c r="A13" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T08</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculadora de Aplicação</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T08_Calculadora_de_Aplicacao.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-073</x:t>
-        </x:is>
+      <x:c r="A13" s="11" t="str">
+        <x:v>T08</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>Calculadora de Aplicação</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>T08_Calculadora_de_Aplicacao.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>BK-073</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
-      <x:c r="A14" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T09</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Estoque</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem recebida</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T09_Estoque.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-078</x:t>
-        </x:is>
+      <x:c r="A14" s="10" t="str">
+        <x:v>T09</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Estoque</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>Imagem recebida</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="str">
+        <x:v>T09_Estoque.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E14" s="10" t="str">
+        <x:v>BK-078</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
-      <x:c r="A15" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Produção</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2 arquivos idênticos</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T10_Producao.png + ChatGPT Image 12 de set. de 2026, 20_48_11.png; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-081</x:t>
-        </x:is>
+      <x:c r="A15" s="11" t="str">
+        <x:v>T10</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>Produção</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>2 arquivos idênticos</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>T10_Producao.png + ChatGPT Image 12 de set. de 2026, 20_48_11.png; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>BK-081</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
-      <x:c r="A16" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T11</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Compras</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contrato recebido; visual aprovado a localizar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Q_CEI_Tela_11; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-086</x:t>
-        </x:is>
+      <x:c r="A16" s="10" t="str">
+        <x:v>T11</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>Compras</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>Contrato recebido; visual aprovado a localizar</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>Q_CEI_Tela_11; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E16" s="10" t="str">
+        <x:v>BK-086</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
-      <x:c r="A17" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Projeções</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem e contrato</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T12_Projecoes.png + R_CEI_Tela_12; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-096</x:t>
-        </x:is>
+      <x:c r="A17" s="11" t="str">
+        <x:v>T12</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>Projeções</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>Imagem e contrato</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>T12_Projecoes.png + R_CEI_Tela_12; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>BK-096</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
-      <x:c r="A18" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T13</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lançamentos e Pendências</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem e contrato</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T13_Lancamentos_e_Pendencias.png + S_CEI_Tela_13; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-099</x:t>
-        </x:is>
+      <x:c r="A18" s="10" t="str">
+        <x:v>T13</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>Lançamentos e Pendências</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>Imagem e contrato</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>T13_Lancamentos_e_Pendencias.png + S_CEI_Tela_13; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E18" s="10" t="str">
+        <x:v>BK-099</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
-      <x:c r="A19" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T14</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Alertas</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem e contrato</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T14_Alertas.png + T_CEI_Tela_14; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-101</x:t>
-        </x:is>
+      <x:c r="A19" s="11" t="str">
+        <x:v>T14</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="str">
+        <x:v>Alertas</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="str">
+        <x:v>Imagem e contrato</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="str">
+        <x:v>T14_Alertas.png + T_CEI_Tela_14; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str">
+        <x:v>BK-101</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
-      <x:c r="A20" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T15</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Importações e Integrações</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem e contrato</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T15_Importacoes_e_Integracoes.png + U_CEI_Tela_15; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-052</x:t>
-        </x:is>
+      <x:c r="A20" s="10" t="str">
+        <x:v>T15</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>Importações e Integrações</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>Imagem e contrato</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>T15_Importacoes_e_Integracoes.png + U_CEI_Tela_15; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E20" s="10" t="str">
+        <x:v>BK-052</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
-      <x:c r="A21" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T16</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Parâmetros</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem e contrato</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T16_Parametros.png + V_Mockup_Tela_16 + W_CEI_Tela_16; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-037</x:t>
-        </x:is>
+      <x:c r="A21" s="11" t="str">
+        <x:v>T16</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="str">
+        <x:v>Parâmetros</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="str">
+        <x:v>Imagem e contrato</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="str">
+        <x:v>T16_Parametros.png + V_Mockup_Tela_16 + W_CEI_Tela_16; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str">
+        <x:v>BK-037</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
-      <x:c r="A22" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T17</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B22" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Usuários</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imagem e contrato</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D22" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T17_Usuarios.png + X_Mockup_Tela_17 + Y_CEI_Tela_17; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E22" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-035</x:t>
-        </x:is>
+      <x:c r="A22" s="10" t="str">
+        <x:v>T17</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>Usuários</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>Imagem e contrato</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="str">
+        <x:v>T17_Usuarios.png + X_Mockup_Tela_17 + Y_CEI_Tela_17; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E22" s="10" t="str">
+        <x:v>BK-035</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
-      <x:c r="A23" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sem número confirmado</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B23" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Aplicações</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C23" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Referência aprovada a localizar no pacote</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D23" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Menu + T08; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-074</x:t>
-        </x:is>
+      <x:c r="A23" s="11" t="str">
+        <x:v>Sem número confirmado</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>Aplicações</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>Referência aprovada a localizar no pacote</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>Menu + T08; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str">
+        <x:v>BK-074</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
-      <x:c r="A24" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bloco a localizar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B24" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pricing / preço e margem</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Localizar referência funcional/visual aprovada</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D24" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">M-021..M-023; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E24" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-075</x:t>
-        </x:is>
+      <x:c r="A24" s="10" t="str">
+        <x:v>Bloco a localizar</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str">
+        <x:v>Pricing / preço e margem</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>Localizar referência funcional/visual aprovada</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="str">
+        <x:v>M-021..M-023; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E24" s="10" t="str">
+        <x:v>BK-075</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
-      <x:c r="A25" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bloco a localizar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B25" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Logística</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C25" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Localizar referência funcional/visual aprovada</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D25" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">M-013..M-016; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E25" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-076</x:t>
-        </x:is>
+      <x:c r="A25" s="11" t="str">
+        <x:v>Bloco a localizar</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>Logística</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>Localizar referência funcional/visual aprovada</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>M-013..M-016; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str">
+        <x:v>BK-076</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
-      <x:c r="A26" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Escopo a detalhar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B26" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Produtos, Simuladores e Relatórios</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C26" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Localizar referência funcional/visual aprovada</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D26" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">T12/T13; fechamento vigente (função/fonte)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E26" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BK-103</x:t>
-        </x:is>
+      <x:c r="A26" s="10" t="str">
+        <x:v>Escopo a detalhar</x:v>
+      </x:c>
+      <x:c r="B26" s="10" t="str">
+        <x:v>Produtos, Simuladores e Relatórios</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>Localizar referência funcional/visual aprovada</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="str">
+        <x:v>T12/T13; fechamento vigente (função/fonte)</x:v>
+      </x:c>
+      <x:c r="E26" s="10" t="str">
+        <x:v>BK-103</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d93b637c97a4068"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f1c54c19ce24cb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R0b92ed591fed4f99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R41bdbb3be8314419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R8e748c5c297d43b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Racebe127eac54b99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R3f083ed1f1434dd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rf13b9a3188c942dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rc652b006bf9f472d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R2d41f63a62cd481f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.07165354330708662</x:v>
+        <x:v>0.07204724409448819</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -673,7 +673,7 @@
       </x:c>
       <x:c r="C14" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.36562500000000003</x:v>
+        <x:v>0.36875</x:v>
       </x:c>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2" t="str">
@@ -1499,9 +1499,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="16" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="str"/>
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="str">
+        <x:v>Mapa em docs/evidence/APPLICATION-RULE-D003A-2026-09-20.md: DRE/fluxo sem ligação de produção; faltam fonte de aportes/resgates e saldo Itaú transferível. Regra e tela preservadas.</x:v>
+      </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>Majucau / Financeiro</x:v>
       </x:c>
@@ -1518,7 +1520,7 @@
       </x:c>
       <x:c r="N12" s="10" t="n">
         <x:f>F12*G12</x:f>
-        <x:v>0.25</x:v>
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="72" customHeight="1">
@@ -6732,7 +6734,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d154634219a4a34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re05dce0d27724d71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9943,7 +9945,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1752f7c26284cf9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d4cbfe0312349e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10368,7 +10370,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f1c54c19ce24cb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R395a79f2e7d44ee4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R3f083ed1f1434dd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rf13b9a3188c942dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rc652b006bf9f472d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R2d41f63a62cd481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rb856a891e9f7496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R7556482500224e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R8661690043624694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rc02c776acf824a25"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -185,7 +185,7 @@
         <x:color rgb="FFA12622"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE4E0"/>
         </x:patternFill>
       </x:fill>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.07204724409448819</x:v>
+        <x:v>0.0736220472440945</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -694,7 +694,7 @@
       </x:c>
       <x:c r="C15" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.022222222222222223</x:v>
       </x:c>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 11/10/2026: 6 concluídas, 10 em andamento e 111 não iniciadas. Estimativa média: 7,2%; restantes 92,8%. BK-001 aguarda decisão sobre arquivos originais. Regra definida não equivale a implementação concluída.</x:v>
+        <x:v>Backlog em 11/10/2026: 6 concluídas, 11 em andamento e 110 não iniciadas. Estimativa: 7,4%; restante: 92,6%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -2261,15 +2261,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E30" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F30" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="12" t="str"/>
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>Mapa inicial em docs/evidence/THREAT-MODEL-INITIAL-2026-10-11.md: ativos, riscos, controles e verificações propostas. Revisão estática, sem testes; falta mapear todas as fontes, implementar controles e validar.</x:v>
+      </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>Segurança + Arquitetura</x:v>
       </x:c>
@@ -2288,7 +2290,7 @@
       </x:c>
       <x:c r="N30" s="10" t="n">
         <x:f>F30*G30</x:f>
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="72" customHeight="1">
@@ -6734,7 +6736,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re05dce0d27724d71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b563e57f345464c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9945,7 +9947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d4cbfe0312349e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fc68f0b44e147b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10370,7 +10372,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R395a79f2e7d44ee4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0d6b7c272a34be9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rb856a891e9f7496d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R7556482500224e88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R8661690043624694"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rc02c776acf824a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R11680138251a46ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R75ffe39dd94e4bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R358cb6065dc040c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rcffc666f27c94a1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.0736220472440945</x:v>
+        <x:v>0.07440944881889765</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -694,7 +694,7 @@
       </x:c>
       <x:c r="C15" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
-        <x:v>0.022222222222222223</x:v>
+        <x:v>0.03333333333333333</x:v>
       </x:c>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2" t="str">
@@ -2267,10 +2267,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="16" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>Mapa inicial em docs/evidence/THREAT-MODEL-INITIAL-2026-10-11.md: ativos, riscos, controles e verificações propostas. Revisão estática, sem testes; falta mapear todas as fontes, implementar controles e validar.</x:v>
+        <x:v>Falhas controladas securetemp/csvstream e go vet passaram; CI #410 aprovada. Faltam outras falhas, VM limpa, rede e perfis. Detalhes no mapa de riscos.</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>Segurança + Arquitetura</x:v>
@@ -2290,7 +2290,7 @@
       </x:c>
       <x:c r="N30" s="10" t="n">
         <x:f>F30*G30</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="72" customHeight="1">
@@ -6736,7 +6736,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b563e57f345464c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05283bebfd944f3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9947,7 +9947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fc68f0b44e147b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4d91f56e6824e2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10372,7 +10372,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0d6b7c272a34be9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R328b2f0c4b6641b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R11680138251a46ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R75ffe39dd94e4bde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R358cb6065dc040c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rcffc666f27c94a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R9ffa37698abd4b09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R4774c27727de4927"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R86ca7b5283c84d4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R632a0339bb984168"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -185,7 +185,7 @@
         <x:color rgb="FFA12622"/>
       </x:font>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFDE4E0"/>
         </x:patternFill>
       </x:fill>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.07440944881889765</x:v>
+        <x:v>0.07480314960629922</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -755,7 +755,7 @@
       </x:c>
       <x:c r="C18" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A18)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A18)</x:f>
-        <x:v>0.03666666666666667</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D18" s="2"/>
       <x:c r="E18" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 11/10/2026: 6 concluídas, 11 em andamento e 110 não iniciadas. Estimativa: 7,4%; restante: 92,6%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 11/10/2026: 6 concluídas, 11 em andamento e 110 não iniciadas. Estimativa: 7,5%; restante: 92,5%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1282,7 +1282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>Inventário histórico registra 16 PNGs, 15 imagens únicas, 20 abas, T10 duplicada e materiais ausentes; a extração tem 20 entradas de aba e as versões v0/v1/v2 estão preservadas. Os hashes dos originais constam em FONTES.md, mas sources/private/material-original não existe neste checkout e os nomes exatos não foram encontrados em Downloads. A responsável foi consultada se enviará os originais ou aceita hashes/extrações; resposta pendente. BK-001 permanece aberta até a decisão.</x:v>
+        <x:v>Extração existe em docs/planejamento/work/source_extract/: workbook.json representa 20 abas e manifest.json conserva 17 itens/hashes históricos. Os 17 binários originais não foram localizados; a correspondência da extração não foi comprovada. Aceite aguarda os originais ou aprovação da responsável.</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
         <x:v>Produto + UX</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="H12" s="12" t="str">
-        <x:v>Mapa em docs/evidence/APPLICATION-RULE-D003A-2026-09-20.md: DRE/fluxo sem ligação de produção; faltam fonte de aportes/resgates e saldo Itaú transferível. Regra e tela preservadas.</x:v>
+        <x:v>Mapa em docs/evidence/APPLICATION-RULE-D003A-2026-09-20.md: DRE/fluxo sem ligação de produção; faltam fonte de aportes/resgates e saldo Itaú transferível. A responsável reiterou em 11/10/2026 que se preserve a estrutura da calculadora enviada; qualquer mapeamento ainda incerto aguarda confirmação. Regra e tela preservadas.</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>Majucau / Financeiro</x:v>
@@ -2270,7 +2270,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>Falhas controladas securetemp/csvstream e go vet passaram; CI #410 aprovada. Faltam outras falhas, VM limpa, rede e perfis. Detalhes no mapa de riscos.</x:v>
+        <x:v>Mapa e testes controlados em docs/evidence/THREAT-MODEL-INITIAL-2026-10-11.md. Testes de securetemp/csvstream, go vet e diff check locais passaram; CI #410 passou nos jobs backlog, Windows e PostgreSQL (Go, vet, análise de vulnerabilidades, builds, SBOM, smoke do instalador e consolidação). BK-024 continua em andamento: faltam outras falhas controladas, completar o mapa de riscos e validar VM limpa, rede e acesso por perfil.</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>Segurança + Arquitetura</x:v>
@@ -3005,9 +3005,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G47" s="17" t="n">
-        <x:v>0.55</x:v>
-      </x:c>
-      <x:c r="H47" s="12" t="str"/>
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H47" s="12" t="str">
+        <x:v>60% — filtros de situação por rota e falha segura quando a última página é desconhecida; evidência em docs/evidence/BLING-PAGINATION-CONTRACT-2026-10-11.md. Resposta e cursor da conta real seguem sem homologação.</x:v>
+      </x:c>
       <x:c r="I47" s="11" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -3026,7 +3028,7 @@
       </x:c>
       <x:c r="N47" s="11" t="n">
         <x:f>F47*G47</x:f>
-        <x:v>0.55</x:v>
+        <x:v>0.6</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="72" customHeight="1">
@@ -6736,7 +6738,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05283bebfd944f3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb617f7ee2554b23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9947,7 +9949,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4d91f56e6824e2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae13ae6c7d144eca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10372,7 +10374,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R328b2f0c4b6641b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff57fc35eebc4902"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R9ffa37698abd4b09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R4774c27727de4927"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R86ca7b5283c84d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R632a0339bb984168"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Ra0cce655c164412b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R870396d28d3840e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R9809f63334fe4564"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R8d4ebadb649e41a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2270,7 +2270,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>Mapa e testes controlados em docs/evidence/THREAT-MODEL-INITIAL-2026-10-11.md. Testes de securetemp/csvstream, go vet e diff check locais passaram; CI #410 passou nos jobs backlog, Windows e PostgreSQL (Go, vet, análise de vulnerabilidades, builds, SBOM, smoke do instalador e consolidação). BK-024 continua em andamento: faltam outras falhas controladas, completar o mapa de riscos e validar VM limpa, rede e acesso por perfil.</x:v>
+        <x:v>Mapa e testes controlados em docs/evidence/THREAT-MODEL-INITIAL-2026-10-11.md. Busca estática adicional confirma CSV por linha, Bling com decoder direto e limite de 4 MiB/100 registros por página, e consultas de linhas com Rows.Next(); leituras completas restantes têm limites explícitos. BK-024 permanece em 30% porque ainda faltam falhas controladas, fechar o mapa de riscos e validar VM limpa, rede, disco cheio/ACL e acesso por perfil.</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>Segurança + Arquitetura</x:v>
@@ -6738,7 +6738,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb617f7ee2554b23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7758b7ed2a09412c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9949,7 +9949,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae13ae6c7d144eca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf87e6630bb94629"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10374,7 +10374,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff57fc35eebc4902"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R153e93b2abc34af0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Ra0cce655c164412b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R870396d28d3840e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R9809f63334fe4564"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R8d4ebadb649e41a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Raa99502c4f464156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R2f4327cad83a4ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R203491e94d3d4d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R5aa69ee7065b4b0b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -185,7 +185,7 @@
         <x:color rgb="FFA12622"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE4E0"/>
         </x:patternFill>
       </x:fill>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.07480314960629922</x:v>
+        <x:v>0.07519685039370078</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -694,7 +694,7 @@
       </x:c>
       <x:c r="C15" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
-        <x:v>0.03333333333333333</x:v>
+        <x:v>0.03888888888888889</x:v>
       </x:c>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2" t="str">
@@ -2267,10 +2267,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="16" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>Mapa e testes controlados em docs/evidence/THREAT-MODEL-INITIAL-2026-10-11.md. Busca estática adicional confirma CSV por linha, Bling com decoder direto e limite de 4 MiB/100 registros por página, e consultas de linhas com Rows.Next(); leituras completas restantes têm limites explícitos. BK-024 permanece em 30% porque ainda faltam falhas controladas, fechar o mapa de riscos e validar VM limpa, rede, disco cheio/ACL e acesso por perfil.</x:v>
+        <x:v>ACL validada no Windows de desenvolvimento; faltam instalador com conta/credencial do worker e ensaio em VM. BK-024 parcial.</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>Segurança + Arquitetura</x:v>
@@ -2290,7 +2290,7 @@
       </x:c>
       <x:c r="N30" s="10" t="n">
         <x:f>F30*G30</x:f>
-        <x:v>0.3</x:v>
+        <x:v>0.35</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="72" customHeight="1">
@@ -6738,7 +6738,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7758b7ed2a09412c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58f6cac07e874001"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9949,7 +9949,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf87e6630bb94629"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ff58e4245449b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10374,7 +10374,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R153e93b2abc34af0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf44bd5fef2694e16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Raa99502c4f464156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R2f4327cad83a4ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R203491e94d3d4d40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R5aa69ee7065b4b0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R35ea10762ea14e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Ra6547fb4b6e44d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rf9f4ce64802d4566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R06f552cebd62410a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -535,7 +535,7 @@
       </x:c>
       <x:c r="B7" s="22" t="n">
         <x:f>SUMIFS('Tarefas'!$M$6:$M$132,'Tarefas'!$D$6:$D$132,"Planejamento")</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>Com evidência de aceite</x:v>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.07519685039370078</x:v>
+        <x:v>0.08307086614173227</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -615,7 +615,7 @@
       </x:c>
       <x:c r="B11" s="22" t="n">
         <x:f>COUNTIFS('Tarefas'!$E$6:$E$132,"Concluída",'Tarefas'!$H$6:$H$132,"&lt;&gt;")</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>Contagem de entregas concluídas</x:v>
@@ -673,7 +673,7 @@
       </x:c>
       <x:c r="C14" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.36875</x:v>
+        <x:v>0.43125</x:v>
       </x:c>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 11/10/2026: 6 concluídas, 11 em andamento e 110 não iniciadas. Estimativa: 7,5%; restante: 92,5%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 11/10/2026: 7 concluídas, 10 em andamento e 110 não iniciadas. Estimativa: 8,3%; restante: 91,7%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1273,34 +1273,34 @@
         <x:v>Planejamento</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>Em andamento</x:v>
+        <x:v>Concluída</x:v>
       </x:c>
       <x:c r="F7" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>Extração existe em docs/planejamento/work/source_extract/: workbook.json representa 20 abas e manifest.json conserva 17 itens/hashes históricos. Os 17 binários originais não foram localizados; a correspondência da extração não foi comprovada. Aceite aguarda os originais ou aprovação da responsável.</x:v>
+        <x:v>Concluída 11/10: originais/cópias conferidos 17/17 por nome, tamanho e hash; ZIP intacto. Extração: 20 abas. Mockups: 19 hashes e 3 duplicatas conferidos. Detalhes: docs/planejamento/FONTES.md.</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
         <x:v>Produto + UX</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str">
-        <x:v>Aguardar orientação sobre os originais: envio para arquivo privado local ou aceitação de hashes e extrações como suficientes.</x:v>
+        <x:v>Concluído: pacote original preservado e conferido. Pendências sobre conteúdo/regras permanecem nas tarefas técnicas correspondentes.</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
         <x:v>docs/planejamento/FONTES.md; docs/source/README.md; docs/planejamento/work/source_extract; revision_v1.json; revision_v2.json</x:v>
       </x:c>
       <x:c r="M7" s="11" t="n">
         <x:f>IF(AND(E7="Concluída",H7&lt;&gt;""),F7,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N7" s="11" t="n">
         <x:f>F7*G7</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
@@ -6738,7 +6738,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58f6cac07e874001"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06edb995382b4ee1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9949,7 +9949,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ff58e4245449b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb03bd6717a814fe7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10374,7 +10374,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf44bd5fef2694e16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf256ffd9923437e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R35ea10762ea14e9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Ra6547fb4b6e44d6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rf9f4ce64802d4566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R06f552cebd62410a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rf153bb70f24a486d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R51b9d8a25c8044fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Re57625f93b7e4bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R2f301720f458479e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.08307086614173227</x:v>
+        <x:v>0.08346456692913386</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -774,7 +774,7 @@
       </x:c>
       <x:c r="C19" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A19)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="D19" s="2"/>
       <x:c r="E19" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 11/10/2026: 7 concluídas, 10 em andamento e 110 não iniciadas. Estimativa: 8,3%; restante: 91,7%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 11/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,3%; restante: 91,7%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -3655,15 +3655,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E62" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F62" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G62" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="12" t="str"/>
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="H62" s="12" t="str">
+        <x:v>BK-056 parcial (11/10): leitura incremental, com cancelamento e sem totais parciais em falha. Regras D-005-A preservadas; sem integração com fonte ou tela. Ver docs/evidence/AGING-STREAM-READER-2026-10-11.md.</x:v>
+      </x:c>
       <x:c r="I62" s="10" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -3682,7 +3684,7 @@
       </x:c>
       <x:c r="N62" s="10" t="n">
         <x:f>F62*G62</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="72" customHeight="1">
@@ -6738,7 +6740,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06edb995382b4ee1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R302a8fac7dfc4ac0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9949,7 +9951,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb03bd6717a814fe7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R886f67443ca948a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10374,7 +10376,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf256ffd9923437e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ae80c7e809446ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rf153bb70f24a486d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R51b9d8a25c8044fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Re57625f93b7e4bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R2f301720f458479e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rc09ded79ad3241aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R236b73823c7b455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Re27b587fbd0f4059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R45e54dcd63364759"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.08346456692913386</x:v>
+        <x:v>0.08385826771653543</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -715,7 +715,7 @@
       </x:c>
       <x:c r="C16" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A16)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A16)</x:f>
-        <x:v>0.35714285714285715</x:v>
+        <x:v>0.36428571428571427</x:v>
       </x:c>
       <x:c r="D16" s="2"/>
       <x:c r="E16" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 11/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,3%; restante: 91,7%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 11/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,4%; restante: 91,6%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -2567,9 +2567,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G37" s="17" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="H37" s="12" t="str"/>
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="H37" s="12" t="str">
+        <x:v>e4e76cb: referência de erro ligada ao request_id do log; CI 38169879308 passou nos 4 jobs. Pendente conferência visual e ACL dos logs em instalação/VM.</x:v>
+      </x:c>
       <x:c r="I37" s="11" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -2586,7 +2588,7 @@
       </x:c>
       <x:c r="N37" s="11" t="n">
         <x:f>F37*G37</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.85</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="72" customHeight="1">
@@ -6740,7 +6742,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R302a8fac7dfc4ac0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03f2955eec504ef8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9951,7 +9953,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R886f67443ca948a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4336187e61cc4090"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10376,7 +10378,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ae80c7e809446ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20061938d9404256"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rc09ded79ad3241aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R236b73823c7b455d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Re27b587fbd0f4059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R45e54dcd63364759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R6bf3629b5e384616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R2b619b2127ff4391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R6d24a2770c3f4f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R3ea075b669084eeb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.08385826771653543</x:v>
+        <x:v>0.084251968503937</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -755,7 +755,7 @@
       </x:c>
       <x:c r="C18" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A18)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A18)</x:f>
-        <x:v>0.04</x:v>
+        <x:v>0.043333333333333335</x:v>
       </x:c>
       <x:c r="D18" s="2"/>
       <x:c r="E18" s="2" t="str">
@@ -3007,10 +3007,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G47" s="17" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
-        <x:v>60% — filtros de situação por rota e falha segura quando a última página é desconhecida; evidência em docs/evidence/BLING-PAGINATION-CONTRACT-2026-10-11.md. Resposta e cursor da conta real seguem sem homologação.</x:v>
+        <x:v>65% — cabeçalho JWT enable-jwt:1 em OAuth e chamadas autenticadas; filtros de situação por rota e falha segura quando a última página é desconhecida. CI 38172628938 passou. Resposta real e cursor seguem sem homologação; evidências em docs/evidence/BLING-JWT-MIGRATION-2026-10-11.md e BLING-PAGINATION-CONTRACT-2026-10-11.md.</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
         <x:v>Engenharia</x:v>
@@ -3030,7 +3030,7 @@
       </x:c>
       <x:c r="N47" s="11" t="n">
         <x:f>F47*G47</x:f>
-        <x:v>0.6</x:v>
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="72" customHeight="1">
@@ -6742,7 +6742,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03f2955eec504ef8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cc8214069ce470f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9953,7 +9953,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4336187e61cc4090"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R671d08d1ef4d4b5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10378,7 +10378,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20061938d9404256"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d91042e651247c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R6bf3629b5e384616"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R2b619b2127ff4391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R6d24a2770c3f4f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R3ea075b669084eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rfbee9ac8a2af4115"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rbeab9ed6d5ae4f3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R9804101985bf416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rffe7f9ba6d964fef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.084251968503937</x:v>
+        <x:v>0.08464566929133858</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -673,7 +673,7 @@
       </x:c>
       <x:c r="C14" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.43125</x:v>
+        <x:v>0.43437500000000007</x:v>
       </x:c>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 11/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,4%; restante: 91,6%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 11/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,5%; restante: 91,5%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1753,9 +1753,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="16" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="H18" s="12" t="str"/>
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="H18" s="12" t="str">
+        <x:v>15%: Matriz T13–T15; exportação aprovada; rota e escopo pendentes. Ver auditoria ACTION-EXPORT-STATIC-AUDIT-2026-10-11.</x:v>
+      </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>Majucau + UX</x:v>
       </x:c>
@@ -1772,7 +1774,7 @@
       </x:c>
       <x:c r="N18" s="10" t="n">
         <x:f>F18*G18</x:f>
-        <x:v>0.1</x:v>
+        <x:v>0.15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="72" customHeight="1">
@@ -6742,7 +6744,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cc8214069ce470f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0fa190a840b498f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9953,7 +9955,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R671d08d1ef4d4b5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe809852b5834292"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10378,7 +10380,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d91042e651247c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc04beebe2ab4a89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rfbee9ac8a2af4115"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rbeab9ed6d5ae4f3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R9804101985bf416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rffe7f9ba6d964fef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rde3351b81e284cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Ra723b471ab40475b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R27763a68fc154454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rf33fd0b6fd69478e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.08464566929133858</x:v>
+        <x:v>0.08543307086614173</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -673,7 +673,7 @@
       </x:c>
       <x:c r="C14" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.43437500000000007</x:v>
+        <x:v>0.44062500000000004</x:v>
       </x:c>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2" t="str">
@@ -1753,10 +1753,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="16" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="H18" s="12" t="str">
-        <x:v>15%: Matriz T13–T15; exportação aprovada; rota e escopo pendentes. Ver auditoria ACTION-EXPORT-STATIC-AUDIT-2026-10-11.</x:v>
+        <x:v>25%: T02–T07/T13–T15 mapeadas; Excel com tabela e data da tela aprovado para T13–T15. Faltam filtros/escopo, rota e detalhes. Ver auditoria.</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>Majucau + UX</x:v>
@@ -1774,7 +1774,7 @@
       </x:c>
       <x:c r="N18" s="10" t="n">
         <x:f>F18*G18</x:f>
-        <x:v>0.15</x:v>
+        <x:v>0.25</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="72" customHeight="1">
@@ -6744,7 +6744,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0fa190a840b498f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29a9d811ad5346c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9955,7 +9955,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe809852b5834292"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d304d8192e45da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10380,7 +10380,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc04beebe2ab4a89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4ae4f17e9cc498e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Rde3351b81e284cd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Ra723b471ab40475b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R27763a68fc154454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rf33fd0b6fd69478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R879c42bd308b4380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Refdbdd9cd4774c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R432cb8e25f2e467e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rc82b58adabc947e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -475,7 +475,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Status atualizado em 11/10/2026 | fechamento funcional de 13/09/2026</x:v>
+        <x:v>Status atualizado em 12/10/2026 | fechamento funcional de 13/09/2026</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.08543307086614173</x:v>
+        <x:v>0.08645669291338581</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -673,7 +673,7 @@
       </x:c>
       <x:c r="C14" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A14)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A14)</x:f>
-        <x:v>0.44062500000000004</x:v>
+        <x:v>0.446875</x:v>
       </x:c>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2" t="str">
@@ -755,7 +755,7 @@
       </x:c>
       <x:c r="C18" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A18)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A18)</x:f>
-        <x:v>0.043333333333333335</x:v>
+        <x:v>0.04533333333333334</x:v>
       </x:c>
       <x:c r="D18" s="2"/>
       <x:c r="E18" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 11/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,5%; restante: 91,5%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 12/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,6%; restante: 91,4%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1753,10 +1753,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="16" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H18" s="12" t="str">
-        <x:v>25%: T02–T07/T13–T15 mapeadas; Excel com tabela e data da tela aprovado para T13–T15. Faltam filtros/escopo, rota e detalhes. Ver auditoria.</x:v>
+        <x:v>30%: T02–T07/T13–T15 parcialmente mapeadas. Excel aprovado para T13–T15; falta ligar consulta, rota e autorização.</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>Majucau + UX</x:v>
@@ -1774,7 +1774,7 @@
       </x:c>
       <x:c r="N18" s="10" t="n">
         <x:f>F18*G18</x:f>
-        <x:v>0.25</x:v>
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="72" customHeight="1">
@@ -1797,9 +1797,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="17" t="n">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="H19" s="12" t="str"/>
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="str">
+        <x:v>20%: matriz ADMIN/DIRECTOR alinhada. Login, sessão e aplicação das permissões no worker seguem pendentes.</x:v>
+      </x:c>
       <x:c r="I19" s="11" t="str">
         <x:v>Arquitetura + Segurança</x:v>
       </x:c>
@@ -1816,7 +1818,7 @@
       </x:c>
       <x:c r="N19" s="11" t="n">
         <x:f>F19*G19</x:f>
-        <x:v>0.15</x:v>
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="72" customHeight="1">
@@ -3009,10 +3011,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G47" s="17" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
-        <x:v>65% — cabeçalho JWT enable-jwt:1 em OAuth e chamadas autenticadas; filtros de situação por rota e falha segura quando a última página é desconhecida. CI 38172628938 passou. Resposta real e cursor seguem sem homologação; evidências em docs/evidence/BLING-JWT-MIGRATION-2026-10-11.md e BLING-PAGINATION-CONTRACT-2026-10-11.md.</x:v>
+        <x:v>68%: JWT/retry e leitura de receber, pagar e caixa. Homologação real, fim/cursor e integração da fonte de caixa pendentes.</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
         <x:v>Engenharia</x:v>
@@ -3032,7 +3034,7 @@
       </x:c>
       <x:c r="N47" s="11" t="n">
         <x:f>F47*G47</x:f>
-        <x:v>0.65</x:v>
+        <x:v>0.68</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="72" customHeight="1">
@@ -6744,7 +6746,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29a9d811ad5346c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2cf20d16571428a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9955,7 +9957,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d304d8192e45da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d936a0909544b6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10380,7 +10382,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4ae4f17e9cc498e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa6f0a83a0f54add"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R879c42bd308b4380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Refdbdd9cd4774c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R432cb8e25f2e467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rc82b58adabc947e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R0a7586f48caa4c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R125b726d5bfd406c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rf56007c7b60d401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R9033e452735141c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.08645669291338581</x:v>
+        <x:v>0.08653543307086613</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -755,7 +755,7 @@
       </x:c>
       <x:c r="C18" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A18)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A18)</x:f>
-        <x:v>0.04533333333333334</x:v>
+        <x:v>0.046</x:v>
       </x:c>
       <x:c r="D18" s="2"/>
       <x:c r="E18" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 12/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,6%; restante: 91,4%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 12/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,7%; restante: 91,3%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -3011,10 +3011,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G47" s="17" t="n">
-        <x:v>0.68</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
-        <x:v>68%: JWT/retry e leitura de receber, pagar e caixa. Homologação real, fim/cursor e integração da fonte de caixa pendentes.</x:v>
+        <x:v>69%: JWT/retry; /caixas usa parâmetros documentados e limite local. Homologação real, fim/cursor e integração CAPEX pendentes.</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
         <x:v>Engenharia</x:v>
@@ -3034,7 +3034,7 @@
       </x:c>
       <x:c r="N47" s="11" t="n">
         <x:f>F47*G47</x:f>
-        <x:v>0.68</x:v>
+        <x:v>0.69</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="72" customHeight="1">
@@ -6746,7 +6746,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2cf20d16571428a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f5920101a0f49a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9957,7 +9957,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d936a0909544b6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d8c07171e64eb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10382,7 +10382,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa6f0a83a0f54add"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb7e9c4a20ff4888"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R0a7586f48caa4c38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R125b726d5bfd406c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="Rf56007c7b60d401d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R9033e452735141c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R4d9b1ad4d6f54a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R532732aa4db04d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R7cbd3fb8070a4022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rbdde048432f841a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.08653543307086613</x:v>
+        <x:v>0.09086614173228345</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -715,7 +715,7 @@
       </x:c>
       <x:c r="C16" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A16)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A16)</x:f>
-        <x:v>0.36428571428571427</x:v>
+        <x:v>0.4428571428571429</x:v>
       </x:c>
       <x:c r="D16" s="2"/>
       <x:c r="E16" s="2" t="str">
@@ -952,7 +952,7 @@
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="4" t="str">
-        <x:v>Fechamento de 13/09/2026; decisões posteriores registradas no G0-DECISION-REGISTER.md até 11/10/2026.</x:v>
+        <x:v>Fechamento de 13/09/2026; decisões posteriores registradas no G0-DECISION-REGISTER.md até 12/10/2026.</x:v>
       </x:c>
       <x:c r="B31" s="2"/>
       <x:c r="C31" s="2"/>
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 12/10/2026: 7 concluídas, 11 em andamento e 109 não iniciadas. Estimativa: 8,7%; restante: 91,3%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 12/10/2026: 7 concluídas, 12 em andamento e 108 não iniciadas. Estimativa: 9,1%; restante: 90,9%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -2353,15 +2353,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E32" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F32" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="12" t="str"/>
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>docs/evidence/DEV-ENVIRONMENT-SETUP-2026-10-12.md; scripts/start-prototype.ps1 iniciou o protótipo com PostgreSQL isolado; validação visual/funcional e em máquina limpa pendente</x:v>
+      </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -2378,7 +2380,7 @@
       </x:c>
       <x:c r="N32" s="10" t="n">
         <x:f>F32*G32</x:f>
-        <x:v>0</x:v>
+        <x:v>0.55</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="72" customHeight="1">
@@ -6746,7 +6748,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f5920101a0f49a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d4f9faaa95047fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9957,7 +9959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d8c07171e64eb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37094c9bd03641cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10382,7 +10384,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb7e9c4a20ff4888"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f7600d80e424eec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R4d9b1ad4d6f54a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R532732aa4db04d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R7cbd3fb8070a4022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rbdde048432f841a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Red8383de65c042d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rb567c40c1b644837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R2cdd46836e544f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rcb4c38bf24c845bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.09086614173228345</x:v>
+        <x:v>0.09094488188976377</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -850,7 +850,7 @@
       </x:c>
       <x:c r="C23" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A23)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0016666666666666668</x:v>
       </x:c>
       <x:c r="D23" s="2"/>
       <x:c r="E23" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 12/10/2026: 7 concluídas, 12 em andamento e 108 não iniciadas. Estimativa: 9,1%; restante: 90,9%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 12/10/2026: 7 concluídas, 13 em andamento e 107 não iniciadas. Estimativa: 9,1%; restante: 90,9%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -5671,13 +5671,13 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E108" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F108" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G108" s="16" t="n">
-        <x:v>0</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="H108" s="12" t="str"/>
       <x:c r="I108" s="10" t="str">
@@ -5698,7 +5698,7 @@
       </x:c>
       <x:c r="N108" s="10" t="n">
         <x:f>F108*G108</x:f>
-        <x:v>0</x:v>
+        <x:v>0.01</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="72" customHeight="1">
@@ -6748,7 +6748,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d4f9faaa95047fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e1e050d01c4060"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9959,7 +9959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37094c9bd03641cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f982470130440be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10384,7 +10384,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f7600d80e424eec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb495b3ddc1b24728"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Red8383de65c042d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Rb567c40c1b644837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R2cdd46836e544f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rcb4c38bf24c845bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R90cf62682efe4951"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R5371f03ba03f4e65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R4dab9a89bb744e97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rb9b3b95e93154940"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.09094488188976377</x:v>
+        <x:v>0.09803149606299212</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -694,7 +694,7 @@
       </x:c>
       <x:c r="C15" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
-        <x:v>0.03888888888888889</x:v>
+        <x:v>0.1388888888888889</x:v>
       </x:c>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 12/10/2026: 7 concluídas, 13 em andamento e 107 não iniciadas. Estimativa: 9,1%; restante: 90,9%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 12/10/2026: 7 concluídas, 14 em andamento e 106 não iniciadas. Estimativa: 9,8%; restante: 90,2%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1963,15 +1963,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E23" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F23" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="12" t="str"/>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="H23" s="12" t="str">
+        <x:v>BK-017: limites, contratos, transações e dependências em docs/architecture/GO-MODULAR-BOUNDARIES.md; o worker fecha o pool que cria. O fechamento aguarda BK-016.</x:v>
+      </x:c>
       <x:c r="I23" s="11" t="str">
         <x:v>Arquitetura</x:v>
       </x:c>
@@ -1988,7 +1990,7 @@
       </x:c>
       <x:c r="N23" s="11" t="n">
         <x:f>F23*G23</x:f>
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="72" customHeight="1">
@@ -6748,7 +6750,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e1e050d01c4060"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82facc330e184b3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9959,7 +9961,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f982470130440be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R910a1d69b5db415a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10384,7 +10386,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb495b3ddc1b24728"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ad54d7bd7854919"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R90cf62682efe4951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R5371f03ba03f4e65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R4dab9a89bb744e97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rb9b3b95e93154940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R816e120041ce4fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R649c2397347148cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R100bf687b123449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R244ca79717e448ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -185,7 +185,7 @@
         <x:color rgb="FFA12622"/>
       </x:font>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFDE4E0"/>
         </x:patternFill>
       </x:fill>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.09803149606299212</x:v>
+        <x:v>0.09960629921259842</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -694,7 +694,7 @@
       </x:c>
       <x:c r="C15" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
-        <x:v>0.1388888888888889</x:v>
+        <x:v>0.16111111111111112</x:v>
       </x:c>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2" t="str">
@@ -952,7 +952,7 @@
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="4" t="str">
-        <x:v>Fechamento de 13/09/2026; decisões posteriores registradas no G0-DECISION-REGISTER.md até 12/10/2026.</x:v>
+        <x:v>Fechamento de 13/09/2026; decisões posteriores registradas no G0-DECISION-REGISTER.md até 11/10/2026.</x:v>
       </x:c>
       <x:c r="B31" s="2"/>
       <x:c r="C31" s="2"/>
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 12/10/2026: 7 concluídas, 14 em andamento e 106 não iniciadas. Estimativa: 9,8%; restante: 90,2%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 12/10/2026: 7 concluídas, 15 em andamento e 105 não iniciadas. Estimativa: 10,0%; restante: 90,0%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1289,7 +1289,7 @@
       </x:c>
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str">
-        <x:v>Concluído: pacote original preservado e conferido. Pendências sobre conteúdo/regras permanecem nas tarefas técnicas correspondentes.</x:v>
+        <x:v>Aguardar orientação sobre os originais: envio para arquivo privado local ou aceitação de hashes e extrações como suficientes.</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
         <x:v>docs/planejamento/FONTES.md; docs/source/README.md; docs/planejamento/work/source_extract; revision_v1.json; revision_v2.json</x:v>
@@ -1921,13 +1921,13 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F22" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="16" t="n">
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H22" s="12" t="str"/>
       <x:c r="I22" s="10" t="str">
@@ -1938,7 +1938,7 @@
       </x:c>
       <x:c r="K22" s="10" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>A_Matriz_Mestra; B_Intersecoes; H_Contrato_Dados; Consolidação 13/09/2026, §§6,10–12; Fechamento vigente 13/09/2026, §§1–4</x:v>
+        <x:v>A_Matriz_Mestra; B_Intersecoes; H_Contrato_Dados; Consolidação 13/09/2026, §§6,10–12; Fechamento vigente 13/09/2026, §§1–4; docs/architecture/DOMAIN-CONTEXT-MAP-v1.md</x:v>
       </x:c>
       <x:c r="M22" s="10" t="n">
         <x:f>IF(AND(E22="Concluída",H22&lt;&gt;""),F22,0)</x:f>
@@ -1946,7 +1946,7 @@
       </x:c>
       <x:c r="N22" s="10" t="n">
         <x:f>F22*G22</x:f>
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="72" customHeight="1">
@@ -3018,7 +3018,7 @@
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
-        <x:v>69%: JWT/retry; /caixas usa parâmetros documentados e limite local. Homologação real, fim/cursor e integração CAPEX pendentes.</x:v>
+        <x:v>69%: JWT/retry limitado com classificação de transporte transitório e leitura de receber, pagar e caixa; /caixas usa somente parâmetros documentados e mantém limite local. Homologação real, fim/cursor e integração CAPEX pendentes.</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
         <x:v>Engenharia</x:v>
@@ -4151,7 +4151,9 @@
       <x:c r="G73" s="17" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="H73" s="12" t="str"/>
+      <x:c r="H73" s="12" t="str">
+        <x:v>20%: cards de consulta presentes; fonte técnica oficial identificada, ainda não integrada. Falta homologar a hierarquia real de categorias CAPEX e conciliar movimentações com os relatórios antes de preencher CAPEX pago no mês e acumulado.</x:v>
+      </x:c>
       <x:c r="I73" s="11" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -4162,7 +4164,7 @@
         <x:v>Q-22,F-02</x:v>
       </x:c>
       <x:c r="L73" s="11" t="str">
-        <x:v>T06; Fechamento vigente 13/09/2026, §§2,5</x:v>
+        <x:v>T06; Fechamento vigente 13/09/2026, §§2,5; API Bling v3: GET /caixas, GET /caixas/{idCaixa}, GET /categorias/receitas-despesas; docs/evidence/CAPEX-REPORT-STRUCTURE-REVIEW-2026-10-11.md</x:v>
       </x:c>
       <x:c r="M73" s="11" t="n">
         <x:f>IF(AND(E73="Concluída",H73&lt;&gt;""),F73,0)</x:f>
@@ -6750,7 +6752,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82facc330e184b3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9111e2cfe7ad49a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9961,7 +9963,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R910a1d69b5db415a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cf178b563ba431a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10386,7 +10388,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ad54d7bd7854919"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a806fe5a76e4abf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
+++ b/docs/planejamento/outputs/MAJUCAU_BACKLOG_E_EVOLUCAO_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="R816e120041ce4fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="R649c2397347148cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R100bf687b123449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R244ca79717e448ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="1" r:id="Ra966a77f73514d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarefas" sheetId="2" r:id="Re6352f96d72340a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisoes" sheetId="3" r:id="R6b1b0978db0a43e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rc2e793d57b3b46b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -475,7 +475,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Status atualizado em 12/10/2026 | fechamento funcional de 13/09/2026</x:v>
+        <x:v>Status atualizado em 13/10/2026 | fechamento funcional de 13/09/2026</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -555,7 +555,7 @@
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>SUM('Tarefas'!$N$6:$N$132)/SUM('Tarefas'!$F$6:$F$132)</x:f>
-        <x:v>0.09960629921259842</x:v>
+        <x:v>0.10992125984251969</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Estimativa; não é prontidão</x:v>
@@ -694,7 +694,7 @@
       </x:c>
       <x:c r="C15" s="25" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A15)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A15)</x:f>
-        <x:v>0.16111111111111112</x:v>
+        <x:v>0.16666666666666666</x:v>
       </x:c>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="2" t="str">
@@ -715,7 +715,7 @@
       </x:c>
       <x:c r="C16" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A16)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A16)</x:f>
-        <x:v>0.4428571428571429</x:v>
+        <x:v>0.4928571428571428</x:v>
       </x:c>
       <x:c r="D16" s="2"/>
       <x:c r="E16" s="2" t="str">
@@ -755,7 +755,7 @@
       </x:c>
       <x:c r="C18" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A18)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A18)</x:f>
-        <x:v>0.046</x:v>
+        <x:v>0.10333333333333332</x:v>
       </x:c>
       <x:c r="D18" s="2"/>
       <x:c r="E18" s="2" t="str">
@@ -793,7 +793,7 @@
       </x:c>
       <x:c r="C20" s="26" t="n">
         <x:f>SUMIFS('Tarefas'!$N$6:$N$132,'Tarefas'!$B$6:$B$132,A20)/SUMIFS('Tarefas'!$F$6:$F$132,'Tarefas'!$B$6:$B$132,A20)</x:f>
-        <x:v>0.014285714285714287</x:v>
+        <x:v>0.017857142857142856</x:v>
       </x:c>
       <x:c r="D20" s="2"/>
       <x:c r="E20" s="2" t="str">
@@ -972,7 +972,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="2" t="str">
-        <x:v>Backlog em 12/10/2026: 7 concluídas, 15 em andamento e 105 não iniciadas. Estimativa: 10,0%; restante: 90,0%. É uma estimativa, não prova de prontidão.</x:v>
+        <x:v>Backlog em 13/10/2026: 7 concluídas, 18 em andamento e 102 não iniciadas. Estimativa: 11,0%; restante: 89,0%. É uma estimativa, não prova de prontidão.</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1969,10 +1969,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="17" t="n">
-        <x:v>0.9</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="H23" s="12" t="str">
-        <x:v>BK-017: limites, contratos, transações e dependências em docs/architecture/GO-MODULAR-BOUNDARIES.md; o worker fecha o pool que cria. O fechamento aguarda BK-016.</x:v>
+        <x:v>95%: limites, contratos, composição, transações e dependências estão documentados; a CI verifica as fronteiras de imports. Faltam BK-016 e fechar contratos de módulos quando a propriedade dos fatos estiver definida.</x:v>
       </x:c>
       <x:c r="I23" s="11" t="str">
         <x:v>Arquitetura</x:v>
@@ -1990,7 +1990,7 @@
       </x:c>
       <x:c r="N23" s="11" t="n">
         <x:f>F23*G23</x:f>
-        <x:v>0.9</x:v>
+        <x:v>0.95</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="72" customHeight="1">
@@ -2361,10 +2361,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="16" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H32" s="12" t="str">
-        <x:v>docs/evidence/DEV-ENVIRONMENT-SETUP-2026-10-12.md; scripts/start-prototype.ps1 iniciou o protótipo com PostgreSQL isolado; validação visual/funcional e em máquina limpa pendente</x:v>
+        <x:v>60%: o protótipo foi iniciado com PostgreSQL isolado por scripts/start-prototype.ps1. Faltam validação visual/funcional e ensaio em máquina limpa. Evidência: docs/evidence/DEV-ENVIRONMENT-SETUP-2026-10-12.md.</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>Engenharia</x:v>
@@ -2382,7 +2382,7 @@
       </x:c>
       <x:c r="N32" s="10" t="n">
         <x:f>F32*G32</x:f>
-        <x:v>0.55</x:v>
+        <x:v>0.6</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="72" customHeight="1">
@@ -2399,15 +2399,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E33" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F33" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" s="12" t="str"/>
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="str">
+        <x:v>30%: o worker compõe serviços, limita conexão ao PostgreSQL e encerra de forma controlada; a saúde verifica conexão e quatro tabelas essenciais com códigos sanitizados. CI 38373291264 passou. Faltam permissões completas do worker, configuração de produção e VM limpa. Evidência: docs/evidence/WORKER-DATABASE-SCHEMA-READINESS-2026-10-13.md.</x:v>
+      </x:c>
       <x:c r="I33" s="11" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -2424,7 +2426,7 @@
       </x:c>
       <x:c r="N33" s="11" t="n">
         <x:f>F33*G33</x:f>
-        <x:v>0</x:v>
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="72" customHeight="1">
@@ -3015,10 +3017,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G47" s="17" t="n">
-        <x:v>0.69</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
-        <x:v>69%: JWT/retry limitado com classificação de transporte transitório e leitura de receber, pagar e caixa; /caixas usa somente parâmetros documentados e mantém limite local. Homologação real, fim/cursor e integração CAPEX pendentes.</x:v>
+        <x:v>75%: leitura de receber, pagar e movimentações de caixa com GET limitado; OAuth local via callback HTTPS, state e DPAPI. /caixas usa parâmetros documentados e limite local. Faltam integração/persistência de caixa, homologação da conta, término da paginação e cursor incremental. Evidência: docs/evidence/BLING-OAUTH-LOCAL-RELAY-2026-10-13.md.</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
         <x:v>Engenharia</x:v>
@@ -3038,7 +3040,7 @@
       </x:c>
       <x:c r="N47" s="11" t="n">
         <x:f>F47*G47</x:f>
-        <x:v>0.69</x:v>
+        <x:v>0.75</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="72" customHeight="1">
@@ -3055,15 +3057,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E48" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F48" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G48" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H48" s="12" t="str"/>
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H48" s="12" t="str">
+        <x:v>40%: a ponte do Site lista arquivos em páginas e baixa em fluxo, calcula hash, confere a versão e grava staging em blocos. Faltam credencial e pasta reais do Drive, importação controlada, confirmar leitura somente, agenda diária, medição de carga e VM limpa. Evidência: docs/evidence/DRIVE-STREAMING-IMPORT-2026-10-13.md.</x:v>
+      </x:c>
       <x:c r="I48" s="10" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -3082,7 +3086,7 @@
       </x:c>
       <x:c r="N48" s="10" t="n">
         <x:f>F48*G48</x:f>
-        <x:v>0</x:v>
+        <x:v>0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="72" customHeight="1">
@@ -3099,15 +3103,17 @@
         <x:v>Desenvolvimento</x:v>
       </x:c>
       <x:c r="E49" s="12" t="str">
-        <x:v>Não iniciada</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="F49" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G49" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H49" s="12" t="str"/>
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H49" s="12" t="str">
+        <x:v>40%: estruturas CSV/TSV/JSON são lidas em fluxo com limites e staging; arquivos XLS/XLSX são recusados e nenhuma linha vira fato financeiro antes de aprovação do layout. Faltam contratos aprovados e amostras reais autorizadas, carga e ensaio em VM limpa. Evidência: docs/evidence/DRIVE-STREAMING-IMPORT-2026-10-13.md.</x:v>
+      </x:c>
       <x:c r="I49" s="11" t="str">
         <x:v>Engenharia</x:v>
       </x:c>
@@ -3124,7 +3130,7 @@
       </x:c>
       <x:c r="N49" s="11" t="n">
         <x:f>F49*G49</x:f>
-        <x:v>0</x:v>
+        <x:v>0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="72" customHeight="1">
@@ -4149,10 +4155,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G73" s="17" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="H73" s="12" t="str">
-        <x:v>20%: cards de consulta presentes; fonte técnica oficial identificada, ainda não integrada. Falta homologar a hierarquia real de categorias CAPEX e conciliar movimentações com os relatórios antes de preencher CAPEX pago no mês e acumulado.</x:v>
+        <x:v>25%: cards informativos EBIT, EBITDA e CAPEX permanecem no espaço aprovado, somente para consulta; CAPEX fica fora da tabela e do lucro. O backend ainda não traz valores reais para os cards; faltam homologar categorias/paginação, persistir e conciliar movimentações e fechar a DRE própria. Evidência: docs/evidence/CAPEX-REPORT-DATA-SOURCE-AUDIT-2026-10-11.md.</x:v>
       </x:c>
       <x:c r="I73" s="11" t="str">
         <x:v>Engenharia</x:v>
@@ -4172,7 +4178,7 @@
       </x:c>
       <x:c r="N73" s="11" t="n">
         <x:f>F73*G73</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.25</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="72" customHeight="1">
@@ -6752,7 +6758,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9111e2cfe7ad49a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75dff4762f7c4fe2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9963,7 +9969,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cf178b563ba431a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fe250347c754326"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10388,7 +10394,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a806fe5a76e4abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f99bc3cce244267"/>
   </x:tableParts>
 </x:worksheet>
 </file>